--- a/data/input/ЭТАЛОН защита ВЛ 6кВ ПЕРЕМИТИН.xlsx
+++ b/data/input/ЭТАЛОН защита ВЛ 6кВ ПЕРЕМИТИН.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AI Projects\RelayProtection\rza_calculator\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FB368D-2FC6-4D97-A750-7BD45FBD0307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24F62FC-C911-4B72-A929-1040397F3D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="14340" windowWidth="38400" windowHeight="15345" tabRatio="463" xr2:uid="{EE8DB21C-91D5-42CF-87B8-EEE0625B4B17}"/>
+    <workbookView xWindow="19845" yWindow="1050" windowWidth="38400" windowHeight="19740" tabRatio="463" activeTab="2" xr2:uid="{EE8DB21C-91D5-42CF-87B8-EEE0625B4B17}"/>
   </bookViews>
   <sheets>
     <sheet name="Расчет" sheetId="3" r:id="rId1"/>
@@ -1959,10 +1959,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1972,6 +1977,224 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="39" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2009,12 +2232,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2026,12 +2243,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2087,217 +2298,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="39" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2310,20 +2310,8 @@
     <xf numFmtId="49" fontId="27" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2342,6 +2330,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2469,34 +2469,34 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.4</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.6</c:v>
+                  <c:v>2.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.8</c:v>
+                  <c:v>3.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.2</c:v>
+                  <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.4</c:v>
+                  <c:v>5.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>41.6</c:v>
+                  <c:v>6.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46.800000000000004</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>52</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2511,34 +2511,34 @@
                   <c:v>5478.2608695652179</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1045.0365080501524</c:v>
+                  <c:v>891.95577358326875</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>572.74645249158289</c:v>
+                  <c:v>454.86457853061512</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>394.31272734370668</c:v>
+                  <c:v>304.82500824396641</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300.62212779780572</c:v>
+                  <c:v>229.15214187618625</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>243.05643506948761</c:v>
+                  <c:v>183.56199987721141</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>204.45822779421155</c:v>
+                  <c:v>153.09628526363929</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>176.43800569026689</c:v>
+                  <c:v>131.30137977998902</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>151.91819160635805</c:v>
+                  <c:v>114.93744856736167</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>129.71875066013595</c:v>
+                  <c:v>102.19972160433029</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>112.32956325113049</c:v>
+                  <c:v>92.003242367296878</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2589,34 +2589,34 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.4</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.6</c:v>
+                  <c:v>2.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.8</c:v>
+                  <c:v>3.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.2</c:v>
+                  <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.4</c:v>
+                  <c:v>5.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>41.6</c:v>
+                  <c:v>6.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46.800000000000004</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>52</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2631,34 +2631,34 @@
                   <c:v>3652.1739130434785</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>696.69100536676831</c:v>
+                  <c:v>594.63718238884587</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>381.83096832772191</c:v>
+                  <c:v>303.24305235374339</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>262.8751515624711</c:v>
+                  <c:v>203.21667216264427</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>200.41475186520381</c:v>
+                  <c:v>152.76809458412416</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>162.03762337965841</c:v>
+                  <c:v>122.3746665848076</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>136.30548519614103</c:v>
+                  <c:v>102.06419017575952</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>117.6253371268446</c:v>
+                  <c:v>87.534253186659342</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>101.2787944042387</c:v>
+                  <c:v>76.624965711574447</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>86.479167106757302</c:v>
+                  <c:v>68.133147736220195</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>74.886375500753658</c:v>
+                  <c:v>61.335494911531249</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2713,34 +2713,34 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.4</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.6</c:v>
+                  <c:v>2.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.8</c:v>
+                  <c:v>3.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.2</c:v>
+                  <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.4</c:v>
+                  <c:v>5.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>41.6</c:v>
+                  <c:v>6.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46.800000000000004</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>52</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2832,34 +2832,34 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.4</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.6</c:v>
+                  <c:v>2.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.8</c:v>
+                  <c:v>3.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.2</c:v>
+                  <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.4</c:v>
+                  <c:v>5.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>41.6</c:v>
+                  <c:v>6.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46.800000000000004</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>52</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2952,34 +2952,34 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.4</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.6</c:v>
+                  <c:v>2.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.8</c:v>
+                  <c:v>3.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.2</c:v>
+                  <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.4</c:v>
+                  <c:v>5.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>41.6</c:v>
+                  <c:v>6.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46.800000000000004</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>52</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2991,37 +2991,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>980</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3072,34 +3072,34 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.4</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.6</c:v>
+                  <c:v>2.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.8</c:v>
+                  <c:v>3.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.2</c:v>
+                  <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.4</c:v>
+                  <c:v>5.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>41.6</c:v>
+                  <c:v>6.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46.800000000000004</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>52</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3111,37 +3111,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>74.8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3436,7 +3436,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="10" dropStyle="combo" dx="22" fmlaLink="$C$9" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="18" val="16"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="10" dropStyle="combo" dx="22" fmlaLink="$C$9" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3448,39 +3448,39 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="10" dropStyle="combo" dx="22" fmlaLink="$C$28" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="17" val="16"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="10" dropStyle="combo" dx="22" fmlaLink="$C$28" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$29" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="62" val="59"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$29" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$31" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="20" val="18"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$31" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$32" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="62" val="59"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$32" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$34" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="21" val="18"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$34" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$35" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="63" val="59"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$35" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$37" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="23" val="18"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$37" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$38" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="62" val="59"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$38" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$10" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="61" val="59"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$10" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3488,27 +3488,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$12" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="19" val="18"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$12" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$13" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="60" val="59"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$13" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$15" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="19" val="18"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$15" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$16" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="60" val="59"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$16" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$18" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="21" val="18"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$18" fmlaRange="[1]Провода!$B$2:$E$27" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$19" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="64" val="59"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="22" fmlaLink="$C$19" fmlaRange="[1]Кабели!$B$2:$E$68" noThreeD="1" sel="1" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4583,7 +4583,7 @@
               <a:picLocks noChangeArrowheads="1" noChangeShapeType="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="'1'!C158:D158" spid="_x0000_s3408"/>
+                  <a14:cameraTool cellRange="'1'!C158:D158" spid="_x0000_s3457"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -4661,7 +4661,7 @@
               <a:picLocks noChangeArrowheads="1" noChangeShapeType="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="'1'!B158" spid="_x0000_s3409"/>
+                  <a14:cameraTool cellRange="'1'!B158" spid="_x0000_s3458"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -4739,7 +4739,7 @@
               <a:picLocks noChangeArrowheads="1" noChangeShapeType="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="'1'!C193:D193" spid="_x0000_s3410"/>
+                  <a14:cameraTool cellRange="'1'!C193:D193" spid="_x0000_s3459"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -4817,7 +4817,7 @@
               <a:picLocks noChangeArrowheads="1" noChangeShapeType="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="'1'!B193" spid="_x0000_s3411"/>
+                  <a14:cameraTool cellRange="'1'!B193" spid="_x0000_s3460"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -4895,7 +4895,7 @@
               <a:picLocks noChangeArrowheads="1" noChangeShapeType="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="'1'!A215" spid="_x0000_s3412"/>
+                  <a14:cameraTool cellRange="'1'!A215" spid="_x0000_s3461"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -4973,7 +4973,7 @@
               <a:picLocks noChangeArrowheads="1" noChangeShapeType="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="'1'!R158:S158" spid="_x0000_s3413"/>
+                  <a14:cameraTool cellRange="'1'!R158:S158" spid="_x0000_s3462"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -5051,7 +5051,7 @@
               <a:picLocks noChangeArrowheads="1" noChangeShapeType="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="'1'!R193:S193" spid="_x0000_s3414"/>
+                  <a14:cameraTool cellRange="'1'!R193:S193" spid="_x0000_s3463"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -15861,29 +15861,29 @@
       <c r="E1" s="98"/>
       <c r="F1" s="98"/>
       <c r="G1" s="98"/>
-      <c r="H1" s="295" t="s">
+      <c r="H1" s="223" t="s">
         <v>109</v>
       </c>
-      <c r="I1" s="296"/>
-      <c r="J1" s="296"/>
-      <c r="K1" s="296"/>
-      <c r="L1" s="296"/>
-      <c r="M1" s="296"/>
-      <c r="N1" s="296"/>
-      <c r="O1" s="296"/>
-      <c r="P1" s="296"/>
-      <c r="Q1" s="296"/>
-      <c r="R1" s="296"/>
-      <c r="S1" s="296"/>
-      <c r="T1" s="296"/>
-      <c r="U1" s="296"/>
-      <c r="V1" s="296"/>
-      <c r="W1" s="296"/>
-      <c r="X1" s="296"/>
-      <c r="Y1" s="296"/>
-      <c r="Z1" s="296"/>
-      <c r="AA1" s="296"/>
-      <c r="AB1" s="297"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
+      <c r="L1" s="224"/>
+      <c r="M1" s="224"/>
+      <c r="N1" s="224"/>
+      <c r="O1" s="224"/>
+      <c r="P1" s="224"/>
+      <c r="Q1" s="224"/>
+      <c r="R1" s="224"/>
+      <c r="S1" s="224"/>
+      <c r="T1" s="224"/>
+      <c r="U1" s="224"/>
+      <c r="V1" s="224"/>
+      <c r="W1" s="224"/>
+      <c r="X1" s="224"/>
+      <c r="Y1" s="224"/>
+      <c r="Z1" s="224"/>
+      <c r="AA1" s="224"/>
+      <c r="AB1" s="225"/>
     </row>
     <row r="2" spans="1:28" s="96" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="100" t="s">
@@ -15895,27 +15895,27 @@
       <c r="E2" s="97"/>
       <c r="F2" s="97"/>
       <c r="G2" s="97"/>
-      <c r="H2" s="298"/>
-      <c r="I2" s="299"/>
-      <c r="J2" s="299"/>
-      <c r="K2" s="299"/>
-      <c r="L2" s="299"/>
-      <c r="M2" s="299"/>
-      <c r="N2" s="299"/>
-      <c r="O2" s="299"/>
-      <c r="P2" s="299"/>
-      <c r="Q2" s="299"/>
-      <c r="R2" s="299"/>
-      <c r="S2" s="299"/>
-      <c r="T2" s="299"/>
-      <c r="U2" s="299"/>
-      <c r="V2" s="299"/>
-      <c r="W2" s="299"/>
-      <c r="X2" s="299"/>
-      <c r="Y2" s="299"/>
-      <c r="Z2" s="299"/>
-      <c r="AA2" s="299"/>
-      <c r="AB2" s="300"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="227"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="227"/>
+      <c r="M2" s="227"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="227"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="227"/>
+      <c r="S2" s="227"/>
+      <c r="T2" s="227"/>
+      <c r="U2" s="227"/>
+      <c r="V2" s="227"/>
+      <c r="W2" s="227"/>
+      <c r="X2" s="227"/>
+      <c r="Y2" s="227"/>
+      <c r="Z2" s="227"/>
+      <c r="AA2" s="227"/>
+      <c r="AB2" s="228"/>
     </row>
     <row r="3" spans="1:28" s="96" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="A3" s="100" t="s">
@@ -15928,30 +15928,30 @@
       <c r="E3" s="97"/>
       <c r="F3" s="97"/>
       <c r="G3" s="97"/>
-      <c r="H3" s="301"/>
-      <c r="I3" s="299"/>
-      <c r="J3" s="299"/>
-      <c r="K3" s="299"/>
-      <c r="L3" s="299"/>
-      <c r="M3" s="299"/>
-      <c r="N3" s="302"/>
-      <c r="O3" s="302"/>
-      <c r="P3" s="302"/>
-      <c r="Q3" s="302"/>
-      <c r="R3" s="302"/>
-      <c r="S3" s="302"/>
-      <c r="T3" s="302"/>
-      <c r="U3" s="302"/>
-      <c r="V3" s="302"/>
-      <c r="W3" s="302"/>
-      <c r="X3" s="302"/>
-      <c r="Y3" s="302"/>
-      <c r="Z3" s="302"/>
-      <c r="AA3" s="302"/>
-      <c r="AB3" s="303"/>
+      <c r="H3" s="229"/>
+      <c r="I3" s="227"/>
+      <c r="J3" s="227"/>
+      <c r="K3" s="227"/>
+      <c r="L3" s="227"/>
+      <c r="M3" s="227"/>
+      <c r="N3" s="230"/>
+      <c r="O3" s="230"/>
+      <c r="P3" s="230"/>
+      <c r="Q3" s="230"/>
+      <c r="R3" s="230"/>
+      <c r="S3" s="230"/>
+      <c r="T3" s="230"/>
+      <c r="U3" s="230"/>
+      <c r="V3" s="230"/>
+      <c r="W3" s="230"/>
+      <c r="X3" s="230"/>
+      <c r="Y3" s="230"/>
+      <c r="Z3" s="230"/>
+      <c r="AA3" s="230"/>
+      <c r="AB3" s="231"/>
     </row>
     <row r="4" spans="1:28" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A4" s="293" t="s">
+      <c r="A4" s="253" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="132"/>
@@ -15965,19 +15965,19 @@
       <c r="F4" s="140" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="324" t="s">
+      <c r="H4" s="256" t="s">
         <v>55</v>
       </c>
       <c r="I4" s="212"/>
       <c r="J4" s="213"/>
       <c r="K4" s="213"/>
-      <c r="L4" s="313" t="s">
+      <c r="L4" s="247" t="s">
         <v>140</v>
       </c>
-      <c r="M4" s="314"/>
+      <c r="M4" s="248"/>
     </row>
     <row r="5" spans="1:28" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A5" s="319"/>
+      <c r="A5" s="254"/>
       <c r="B5" s="136"/>
       <c r="C5" s="9">
         <v>401</v>
@@ -15993,17 +15993,17 @@
         <f>VLOOKUP(C5,[1]Реактансы!$A$2:$D$450,4)</f>
         <v>0.57499999999999996</v>
       </c>
-      <c r="H5" s="325"/>
+      <c r="H5" s="257"/>
       <c r="I5" s="170">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="J5" s="171"/>
       <c r="K5" s="171"/>
-      <c r="L5" s="315"/>
-      <c r="M5" s="316"/>
+      <c r="L5" s="249"/>
+      <c r="M5" s="250"/>
     </row>
     <row r="6" spans="1:28" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A6" s="320"/>
+      <c r="A6" s="255"/>
       <c r="B6" s="133"/>
       <c r="C6" s="9"/>
       <c r="D6" s="139" t="s">
@@ -16017,31 +16017,27 @@
         <f>IF(VLOOKUP(C5,[1]Реактансы!$A$2:$K$450,11)&gt;0,VLOOKUP(C5,[1]Реактансы!$A$2:$K$450,11),"---")</f>
         <v>---</v>
       </c>
-      <c r="H6" s="325"/>
-      <c r="I6" s="170">
-        <v>20</v>
-      </c>
+      <c r="H6" s="257"/>
+      <c r="I6" s="170"/>
       <c r="J6" s="171"/>
       <c r="K6" s="171"/>
-      <c r="L6" s="315"/>
-      <c r="M6" s="316"/>
+      <c r="L6" s="249"/>
+      <c r="M6" s="250"/>
     </row>
     <row r="7" spans="1:28" ht="13.5" customHeight="1" thickBot="1">
-      <c r="H7" s="325"/>
-      <c r="I7" s="197">
-        <v>10</v>
-      </c>
+      <c r="H7" s="257"/>
+      <c r="I7" s="197"/>
       <c r="J7" s="208"/>
       <c r="K7" s="208"/>
-      <c r="L7" s="315"/>
-      <c r="M7" s="316"/>
+      <c r="L7" s="249"/>
+      <c r="M7" s="250"/>
     </row>
     <row r="8" spans="1:28" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="321" t="s">
+      <c r="A8" s="217" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="322"/>
-      <c r="C8" s="323"/>
+      <c r="B8" s="218"/>
+      <c r="C8" s="219"/>
       <c r="D8" s="131" t="s">
         <v>5</v>
       </c>
@@ -16051,68 +16047,66 @@
       <c r="F8" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="H8" s="325"/>
-      <c r="I8" s="197">
-        <v>25</v>
-      </c>
+      <c r="H8" s="257"/>
+      <c r="I8" s="197"/>
       <c r="J8" s="208"/>
       <c r="K8" s="208"/>
-      <c r="L8" s="315"/>
-      <c r="M8" s="316"/>
+      <c r="L8" s="249"/>
+      <c r="M8" s="250"/>
     </row>
     <row r="9" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
       <c r="A9" s="66" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="88">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D9" s="94">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E9" s="13">
         <f>VLOOKUP(C9,[1]Провода!$A$1:$E$27,3)</f>
-        <v>0.13100000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F9" s="11">
         <f>VLOOKUP(C9,[1]Провода!$A$1:$E$27,4)</f>
         <v>0.4</v>
       </c>
-      <c r="H9" s="325"/>
+      <c r="H9" s="257"/>
       <c r="I9" s="214"/>
       <c r="J9" s="215"/>
       <c r="K9" s="215"/>
-      <c r="L9" s="317">
+      <c r="L9" s="251">
         <f>SUM(I4:K9)</f>
-        <v>65</v>
-      </c>
-      <c r="M9" s="318"/>
+        <v>250</v>
+      </c>
+      <c r="M9" s="252"/>
     </row>
     <row r="10" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
       <c r="A10" s="66" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="88">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D10" s="95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" s="13">
         <f>VLOOKUP(C10,[1]Кабели!$A$1:$E$68,3)</f>
-        <v>8.666666666666667E-2</v>
+        <v>3.1</v>
       </c>
       <c r="F10" s="11">
         <f>VLOOKUP(C10,[1]Кабели!$A$1:$E$68,4)</f>
-        <v>2.6666666666666668E-2</v>
-      </c>
-      <c r="H10" s="325"/>
+        <v>0.11</v>
+      </c>
+      <c r="H10" s="257"/>
       <c r="I10" s="209" t="s">
         <v>36</v>
       </c>
       <c r="J10" s="206">
         <f>L9/10.38</f>
-        <v>6.262042389210019</v>
+        <v>24.084778420038536</v>
       </c>
       <c r="K10" s="207" t="s">
         <v>144</v>
@@ -16121,11 +16115,11 @@
       <c r="M10" s="141"/>
     </row>
     <row r="11" spans="1:28" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="219" t="s">
+      <c r="A11" s="220" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="220"/>
-      <c r="C11" s="221"/>
+      <c r="B11" s="221"/>
+      <c r="C11" s="222"/>
       <c r="D11" s="131" t="s">
         <v>5</v>
       </c>
@@ -16135,13 +16129,13 @@
       <c r="F11" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="H11" s="325"/>
+      <c r="H11" s="257"/>
       <c r="I11" s="210" t="s">
         <v>46</v>
       </c>
       <c r="J11" s="169">
         <f>0.7*J10</f>
-        <v>4.3834296724470132</v>
+        <v>16.859344894026975</v>
       </c>
       <c r="K11" s="180" t="s">
         <v>144</v>
@@ -16154,20 +16148,20 @@
         <v>3</v>
       </c>
       <c r="C12" s="88">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D12" s="94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="13">
         <f>VLOOKUP(C12,[1]Провода!$A$1:$E$27,3)</f>
-        <v>7.2999999999999995E-2</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F12" s="11">
         <f>VLOOKUP(C12,[1]Провода!$A$1:$E$27,4)</f>
         <v>0.4</v>
       </c>
-      <c r="H12" s="326"/>
+      <c r="H12" s="258"/>
       <c r="I12" s="211" t="s">
         <v>37</v>
       </c>
@@ -16185,26 +16179,26 @@
         <v>4</v>
       </c>
       <c r="C13" s="88">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D13" s="95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="13">
         <f>VLOOKUP(C13,[1]Кабели!$A$1:$E$68,3)</f>
-        <v>0.12333333333333334</v>
+        <v>3.1</v>
       </c>
       <c r="F13" s="11">
         <f>VLOOKUP(C13,[1]Кабели!$A$1:$E$68,4)</f>
-        <v>2.7666666666666669E-2</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="219" t="s">
+      <c r="A14" s="220" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="220"/>
-      <c r="C14" s="221"/>
+      <c r="B14" s="221"/>
+      <c r="C14" s="222"/>
       <c r="D14" s="131" t="s">
         <v>5</v>
       </c>
@@ -16214,13 +16208,13 @@
       <c r="F14" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="H14" s="245" t="s">
+      <c r="H14" s="312" t="s">
         <v>39</v>
       </c>
-      <c r="I14" s="246"/>
-      <c r="J14" s="246"/>
-      <c r="K14" s="246"/>
-      <c r="L14" s="217" t="s">
+      <c r="I14" s="313"/>
+      <c r="J14" s="313"/>
+      <c r="K14" s="313"/>
+      <c r="L14" s="291" t="s">
         <v>75</v>
       </c>
     </row>
@@ -16229,55 +16223,55 @@
         <v>3</v>
       </c>
       <c r="C15" s="88">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D15" s="94">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" s="13">
         <f>VLOOKUP(C15,[1]Провода!$A$1:$E$27,3)</f>
-        <v>7.2999999999999995E-2</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F15" s="11">
         <f>VLOOKUP(C15,[1]Провода!$A$1:$E$27,4)</f>
         <v>0.4</v>
       </c>
-      <c r="H15" s="247"/>
-      <c r="I15" s="248"/>
-      <c r="J15" s="248"/>
-      <c r="K15" s="248"/>
-      <c r="L15" s="218"/>
+      <c r="H15" s="314"/>
+      <c r="I15" s="315"/>
+      <c r="J15" s="315"/>
+      <c r="K15" s="315"/>
+      <c r="L15" s="292"/>
     </row>
     <row r="16" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
       <c r="A16" s="66" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="88">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D16" s="95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="13">
         <f>VLOOKUP(C16,[1]Кабели!$A$1:$E$68,3)</f>
-        <v>0.12333333333333334</v>
+        <v>3.1</v>
       </c>
       <c r="F16" s="11">
         <f>VLOOKUP(C16,[1]Кабели!$A$1:$E$68,4)</f>
-        <v>2.7666666666666669E-2</v>
+        <v>0.11</v>
       </c>
       <c r="H16" s="7"/>
       <c r="K16" s="89">
         <v>6</v>
       </c>
-      <c r="L16" s="218"/>
+      <c r="L16" s="292"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="219" t="s">
+      <c r="A17" s="220" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="220"/>
-      <c r="C17" s="221"/>
+      <c r="B17" s="221"/>
+      <c r="C17" s="222"/>
       <c r="D17" s="131" t="s">
         <v>5</v>
       </c>
@@ -16288,28 +16282,28 @@
         <v>136</v>
       </c>
       <c r="H17" s="7"/>
-      <c r="L17" s="218"/>
+      <c r="L17" s="292"/>
     </row>
     <row r="18" spans="1:13" ht="19.5" customHeight="1">
       <c r="A18" s="66" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="88">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D18" s="94">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18" s="13">
         <f>VLOOKUP(C18,[1]Провода!$A$1:$E$27,3)</f>
-        <v>0.72</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F18" s="11">
         <f>VLOOKUP(C18,[1]Провода!$A$1:$E$27,4)</f>
-        <v>0.29899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H18" s="7"/>
-      <c r="L18" s="218"/>
+      <c r="L18" s="292"/>
     </row>
     <row r="19" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
       <c r="A19" s="172" t="s">
@@ -16317,46 +16311,46 @@
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="87">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D19" s="173">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E19" s="14">
         <f>VLOOKUP(C19,[1]Кабели!$A$1:$E$68,3)</f>
-        <v>4.0666666666666663E-2</v>
+        <v>3.1</v>
       </c>
       <c r="F19" s="12">
         <f>VLOOKUP(C19,[1]Кабели!$A$1:$E$68,4)</f>
-        <v>2.4666666666666667E-2</v>
-      </c>
-      <c r="H19" s="249" t="s">
+        <v>0.11</v>
+      </c>
+      <c r="H19" s="316" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="250"/>
-      <c r="J19" s="250"/>
-      <c r="K19" s="250"/>
+      <c r="I19" s="317"/>
+      <c r="J19" s="317"/>
+      <c r="K19" s="317"/>
       <c r="L19" s="57">
         <f>VLOOKUP(K16,[1]Реле!$A$1:$D$10,4)</f>
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="13.5" thickBot="1">
-      <c r="A20" s="232" t="s">
+      <c r="A20" s="303" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="233"/>
-      <c r="C20" s="233"/>
+      <c r="B20" s="304"/>
+      <c r="C20" s="304"/>
       <c r="D20" s="60">
         <f>SUM(D9:D19)</f>
-        <v>52</v>
-      </c>
-      <c r="H20" s="304" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="232" t="s">
         <v>41</v>
       </c>
-      <c r="I20" s="305"/>
-      <c r="J20" s="305"/>
-      <c r="K20" s="305"/>
+      <c r="I20" s="233"/>
+      <c r="J20" s="233"/>
+      <c r="K20" s="233"/>
       <c r="L20" s="58">
         <f>VLOOKUP(K16,[1]Реле!$A$1:$D$10,3)</f>
         <v>1.1499999999999999</v>
@@ -16364,51 +16358,51 @@
     </row>
     <row r="21" spans="1:13" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="22" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A22" s="251" t="s">
+      <c r="A22" s="318" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="252"/>
-      <c r="C22" s="252"/>
-      <c r="D22" s="253"/>
-      <c r="E22" s="242" t="s">
+      <c r="B22" s="319"/>
+      <c r="C22" s="319"/>
+      <c r="D22" s="320"/>
+      <c r="E22" s="309" t="s">
         <v>143</v>
       </c>
-      <c r="H22" s="282" t="s">
+      <c r="H22" s="235" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="283"/>
-      <c r="J22" s="283"/>
-      <c r="K22" s="283"/>
-      <c r="L22" s="283"/>
-      <c r="M22" s="284"/>
+      <c r="I22" s="236"/>
+      <c r="J22" s="236"/>
+      <c r="K22" s="236"/>
+      <c r="L22" s="236"/>
+      <c r="M22" s="237"/>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1">
-      <c r="A23" s="254"/>
-      <c r="B23" s="255"/>
-      <c r="C23" s="255"/>
-      <c r="D23" s="256"/>
-      <c r="E23" s="243"/>
-      <c r="H23" s="285"/>
-      <c r="I23" s="286"/>
-      <c r="J23" s="286"/>
-      <c r="K23" s="286"/>
-      <c r="L23" s="286"/>
-      <c r="M23" s="287"/>
+      <c r="A23" s="321"/>
+      <c r="B23" s="322"/>
+      <c r="C23" s="322"/>
+      <c r="D23" s="323"/>
+      <c r="E23" s="310"/>
+      <c r="H23" s="238"/>
+      <c r="I23" s="239"/>
+      <c r="J23" s="239"/>
+      <c r="K23" s="239"/>
+      <c r="L23" s="239"/>
+      <c r="M23" s="240"/>
     </row>
     <row r="24" spans="1:13" ht="19.5" thickBot="1">
-      <c r="A24" s="257"/>
-      <c r="B24" s="258"/>
-      <c r="C24" s="258"/>
-      <c r="D24" s="259"/>
-      <c r="E24" s="244"/>
-      <c r="H24" s="240" t="s">
+      <c r="A24" s="324"/>
+      <c r="B24" s="325"/>
+      <c r="C24" s="325"/>
+      <c r="D24" s="326"/>
+      <c r="E24" s="311"/>
+      <c r="H24" s="241" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="241"/>
-      <c r="J24" s="241"/>
+      <c r="I24" s="242"/>
+      <c r="J24" s="242"/>
       <c r="K24" s="68">
         <f>IFERROR('1'!B44*L20,"---")</f>
-        <v>264.4661245850898</v>
+        <v>113.40292587610691</v>
       </c>
       <c r="L24" s="179" t="str">
         <f>IFERROR('1'!P44*L20,"---")</f>
@@ -16422,14 +16416,14 @@
       <c r="A25" s="7"/>
       <c r="D25" s="8"/>
       <c r="E25" s="56"/>
-      <c r="H25" s="240" t="s">
+      <c r="H25" s="241" t="s">
         <v>52</v>
       </c>
-      <c r="I25" s="241"/>
-      <c r="J25" s="241"/>
+      <c r="I25" s="242"/>
+      <c r="J25" s="242"/>
       <c r="K25" s="166">
         <f>J10*L19</f>
-        <v>18.786127167630056</v>
+        <v>72.25433526011561</v>
       </c>
       <c r="L25" s="176"/>
       <c r="M25" s="182" t="s">
@@ -16447,13 +16441,13 @@
         <f>VLOOKUP(D26,[1]Трансформаторы!$A$1:$C$12,3)</f>
         <v>9.68</v>
       </c>
-      <c r="H26" s="234" t="s">
+      <c r="H26" s="244" t="s">
         <v>57</v>
       </c>
-      <c r="I26" s="235"/>
-      <c r="J26" s="235"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
       <c r="K26" s="168">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="L26" s="175"/>
       <c r="M26" s="183" t="s">
@@ -16461,11 +16455,11 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="321" t="s">
+      <c r="A27" s="217" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="322"/>
-      <c r="C27" s="323"/>
+      <c r="B27" s="218"/>
+      <c r="C27" s="219"/>
       <c r="D27" s="131" t="s">
         <v>5</v>
       </c>
@@ -16475,15 +16469,15 @@
       <c r="F27" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="H27" s="234" t="s">
+      <c r="H27" s="244" t="s">
         <v>59</v>
       </c>
-      <c r="I27" s="235"/>
-      <c r="J27" s="308">
+      <c r="I27" s="245"/>
+      <c r="J27" s="246">
         <v>0</v>
       </c>
-      <c r="K27" s="308"/>
-      <c r="L27" s="308"/>
+      <c r="K27" s="246"/>
+      <c r="L27" s="246"/>
       <c r="M27" s="141"/>
     </row>
     <row r="28" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
@@ -16491,28 +16485,28 @@
         <v>3</v>
       </c>
       <c r="C28" s="88">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D28" s="94">
         <v>1</v>
       </c>
       <c r="E28" s="13">
         <f>VLOOKUP(C28,[1]Провода!$A$1:$E$27,3)</f>
-        <v>0.159</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F28" s="11">
         <f>VLOOKUP(C28,[1]Провода!$A$1:$E$27,4)</f>
         <v>0.4</v>
       </c>
-      <c r="H28" s="229" t="s">
+      <c r="H28" s="300" t="s">
         <v>70</v>
       </c>
-      <c r="I28" s="230"/>
-      <c r="J28" s="231">
+      <c r="I28" s="301"/>
+      <c r="J28" s="302">
         <v>15</v>
       </c>
-      <c r="K28" s="231"/>
-      <c r="L28" s="231"/>
+      <c r="K28" s="302"/>
+      <c r="L28" s="302"/>
       <c r="M28" s="142"/>
     </row>
     <row r="29" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
@@ -16520,34 +16514,34 @@
         <v>4</v>
       </c>
       <c r="C29" s="88">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D29" s="95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="13">
         <f>VLOOKUP(C29,[1]Кабели!$A$1:$E$68,3)</f>
-        <v>6.4666666666666664E-2</v>
+        <v>3.1</v>
       </c>
       <c r="F29" s="11">
         <f>VLOOKUP(C29,[1]Кабели!$A$1:$E$68,4)</f>
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="H29" s="282" t="s">
+        <v>0.11</v>
+      </c>
+      <c r="H29" s="235" t="s">
         <v>50</v>
       </c>
-      <c r="I29" s="283"/>
-      <c r="J29" s="283"/>
-      <c r="K29" s="283"/>
-      <c r="L29" s="283"/>
-      <c r="M29" s="284"/>
+      <c r="I29" s="236"/>
+      <c r="J29" s="236"/>
+      <c r="K29" s="236"/>
+      <c r="L29" s="236"/>
+      <c r="M29" s="237"/>
     </row>
     <row r="30" spans="1:13" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="219" t="s">
+      <c r="A30" s="220" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="220"/>
-      <c r="C30" s="221"/>
+      <c r="B30" s="221"/>
+      <c r="C30" s="222"/>
       <c r="D30" s="131" t="s">
         <v>5</v>
       </c>
@@ -16557,39 +16551,39 @@
       <c r="F30" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="H30" s="285"/>
-      <c r="I30" s="286"/>
-      <c r="J30" s="286"/>
-      <c r="K30" s="286"/>
-      <c r="L30" s="286"/>
-      <c r="M30" s="287"/>
+      <c r="H30" s="238"/>
+      <c r="I30" s="239"/>
+      <c r="J30" s="239"/>
+      <c r="K30" s="239"/>
+      <c r="L30" s="239"/>
+      <c r="M30" s="240"/>
     </row>
     <row r="31" spans="1:13" ht="19.5" customHeight="1">
       <c r="A31" s="66" t="s">
         <v>3</v>
       </c>
       <c r="C31" s="88">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D31" s="94">
         <v>1</v>
       </c>
       <c r="E31" s="13">
         <f>VLOOKUP(C31,[1]Провода!$A$1:$E$27,3)</f>
-        <v>0.06</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F31" s="11">
         <f>VLOOKUP(C31,[1]Провода!$A$1:$E$27,4)</f>
         <v>0.4</v>
       </c>
-      <c r="H31" s="240" t="s">
+      <c r="H31" s="241" t="s">
         <v>53</v>
       </c>
-      <c r="I31" s="241"/>
-      <c r="J31" s="241"/>
+      <c r="I31" s="242"/>
+      <c r="J31" s="242"/>
       <c r="K31" s="68">
         <f>J11*1.5</f>
-        <v>6.5751445086705198</v>
+        <v>25.289017341040463</v>
       </c>
       <c r="L31" s="184" t="s">
         <v>31</v>
@@ -16601,24 +16595,24 @@
         <v>4</v>
       </c>
       <c r="C32" s="88">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D32" s="95">
         <v>1</v>
       </c>
       <c r="E32" s="13">
         <f>VLOOKUP(C32,[1]Кабели!$A$1:$E$68,3)</f>
-        <v>6.4666666666666664E-2</v>
+        <v>3.1</v>
       </c>
       <c r="F32" s="11">
         <f>VLOOKUP(C32,[1]Кабели!$A$1:$E$68,4)</f>
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="H32" s="240" t="s">
+        <v>0.11</v>
+      </c>
+      <c r="H32" s="241" t="s">
         <v>54</v>
       </c>
-      <c r="I32" s="241"/>
-      <c r="J32" s="241"/>
+      <c r="I32" s="242"/>
+      <c r="J32" s="242"/>
       <c r="K32" s="166">
         <f>J12*1.5</f>
         <v>33</v>
@@ -16629,11 +16623,11 @@
       <c r="M32" s="8"/>
     </row>
     <row r="33" spans="1:28" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A33" s="219" t="s">
+      <c r="A33" s="220" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="220"/>
-      <c r="C33" s="221"/>
+      <c r="B33" s="221"/>
+      <c r="C33" s="222"/>
       <c r="D33" s="131" t="s">
         <v>5</v>
       </c>
@@ -16643,13 +16637,13 @@
       <c r="F33" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="H33" s="234" t="s">
+      <c r="H33" s="244" t="s">
         <v>58</v>
       </c>
-      <c r="I33" s="235"/>
-      <c r="J33" s="235"/>
+      <c r="I33" s="245"/>
+      <c r="J33" s="245"/>
       <c r="K33" s="216">
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="L33" s="185" t="s">
         <v>31</v>
@@ -16661,31 +16655,31 @@
         <v>3</v>
       </c>
       <c r="C34" s="88">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D34" s="94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="13">
         <f>VLOOKUP(C34,[1]Провода!$A$1:$E$27,3)</f>
-        <v>0.72</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F34" s="11">
         <f>VLOOKUP(C34,[1]Провода!$A$1:$E$27,4)</f>
-        <v>0.29899999999999999</v>
-      </c>
-      <c r="H34" s="234" t="s">
+        <v>0.4</v>
+      </c>
+      <c r="H34" s="244" t="s">
         <v>59</v>
       </c>
-      <c r="I34" s="235"/>
+      <c r="I34" s="245"/>
       <c r="J34" s="174">
         <v>0.5</v>
       </c>
-      <c r="K34" s="307" t="str">
+      <c r="K34" s="243" t="str">
         <f>VLOOKUP(K16,[1]Реле!$A$1:$E$9,5)</f>
         <v>Кратности нет</v>
       </c>
-      <c r="L34" s="307"/>
+      <c r="L34" s="243"/>
       <c r="M34" s="141"/>
     </row>
     <row r="35" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -16693,42 +16687,42 @@
         <v>4</v>
       </c>
       <c r="C35" s="88">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="D35" s="95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="13">
         <f>VLOOKUP(C35,[1]Кабели!$A$1:$E$68,3)</f>
-        <v>5.0999999999999997E-2</v>
+        <v>3.1</v>
       </c>
       <c r="F35" s="11">
         <f>VLOOKUP(C35,[1]Кабели!$A$1:$E$68,4)</f>
-        <v>2.5333333333333333E-2</v>
-      </c>
-      <c r="H35" s="224" t="s">
+        <v>0.11</v>
+      </c>
+      <c r="H35" s="295" t="s">
         <v>77</v>
       </c>
-      <c r="I35" s="225"/>
-      <c r="J35" s="225"/>
-      <c r="K35" s="290">
+      <c r="I35" s="296"/>
+      <c r="J35" s="296"/>
+      <c r="K35" s="272">
         <f>'1'!D30</f>
-        <v>74.886375500753658</v>
-      </c>
-      <c r="L35" s="279" t="str">
+        <v>61.335494911531249</v>
+      </c>
+      <c r="L35" s="267" t="str">
         <f>IFERROR('1'!R30,"---")</f>
         <v>---</v>
       </c>
-      <c r="M35" s="306" t="s">
+      <c r="M35" s="234" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:28" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="219" t="s">
+      <c r="A36" s="220" t="s">
         <v>67</v>
       </c>
-      <c r="B36" s="220"/>
-      <c r="C36" s="221"/>
+      <c r="B36" s="221"/>
+      <c r="C36" s="222"/>
       <c r="D36" s="131" t="s">
         <v>5</v>
       </c>
@@ -16738,39 +16732,39 @@
       <c r="F36" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="H36" s="226"/>
-      <c r="I36" s="225"/>
-      <c r="J36" s="225"/>
-      <c r="K36" s="290"/>
-      <c r="L36" s="279"/>
-      <c r="M36" s="306"/>
+      <c r="H36" s="297"/>
+      <c r="I36" s="296"/>
+      <c r="J36" s="296"/>
+      <c r="K36" s="272"/>
+      <c r="L36" s="267"/>
+      <c r="M36" s="234"/>
     </row>
     <row r="37" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
       <c r="A37" s="66" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="88">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D37" s="94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="13">
         <f>VLOOKUP(C37,[1]Провода!$A$1:$E$27,3)</f>
-        <v>0.36299999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F37" s="11">
         <f>VLOOKUP(C37,[1]Провода!$A$1:$E$27,4)</f>
-        <v>0.28399999999999997</v>
-      </c>
-      <c r="H37" s="280" t="s">
+        <v>0.4</v>
+      </c>
+      <c r="H37" s="268" t="s">
         <v>78</v>
       </c>
-      <c r="I37" s="281"/>
-      <c r="J37" s="281"/>
+      <c r="I37" s="269"/>
+      <c r="J37" s="269"/>
       <c r="K37" s="167">
         <f>'1'!B30</f>
-        <v>112.32956325113049</v>
+        <v>92.003242367296878</v>
       </c>
       <c r="L37" s="178" t="str">
         <f>IFERROR('1'!P30,"---")</f>
@@ -16785,43 +16779,43 @@
         <v>4</v>
       </c>
       <c r="C38" s="88">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D38" s="95">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E38" s="14">
         <f>VLOOKUP(C38,[1]Кабели!$A$1:$E$68,3)</f>
-        <v>6.4666666666666664E-2</v>
+        <v>3.1</v>
       </c>
       <c r="F38" s="12">
         <f>VLOOKUP(C38,[1]Кабели!$A$1:$E$68,4)</f>
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="H38" s="285" t="s">
+        <v>0.11</v>
+      </c>
+      <c r="H38" s="238" t="s">
         <v>50</v>
       </c>
-      <c r="I38" s="286"/>
-      <c r="J38" s="286"/>
-      <c r="K38" s="286"/>
-      <c r="L38" s="286"/>
-      <c r="M38" s="287"/>
+      <c r="I38" s="239"/>
+      <c r="J38" s="239"/>
+      <c r="K38" s="239"/>
+      <c r="L38" s="239"/>
+      <c r="M38" s="240"/>
     </row>
     <row r="39" spans="1:28" ht="18" customHeight="1" thickBot="1">
-      <c r="A39" s="266" t="s">
+      <c r="A39" s="286" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="267"/>
-      <c r="C39" s="267"/>
+      <c r="B39" s="287"/>
+      <c r="C39" s="287"/>
       <c r="D39" s="60">
         <f>SUM(D28:D38)</f>
-        <v>12.3</v>
-      </c>
-      <c r="H39" s="291" t="s">
+        <v>8</v>
+      </c>
+      <c r="H39" s="273" t="s">
         <v>53</v>
       </c>
-      <c r="I39" s="292"/>
-      <c r="J39" s="292"/>
+      <c r="I39" s="274"/>
+      <c r="J39" s="274"/>
       <c r="K39" s="68"/>
       <c r="L39" s="184" t="s">
         <v>31</v>
@@ -16841,10 +16835,10 @@
       <c r="M40" s="141"/>
     </row>
     <row r="41" spans="1:28" ht="20.25" customHeight="1">
-      <c r="H41" s="234" t="s">
+      <c r="H41" s="244" t="s">
         <v>59</v>
       </c>
-      <c r="I41" s="235"/>
+      <c r="I41" s="245"/>
       <c r="J41" s="91"/>
       <c r="K41" s="103"/>
       <c r="L41" s="103"/>
@@ -16867,11 +16861,11 @@
       <c r="B43" s="42"/>
       <c r="C43" s="42"/>
       <c r="D43" s="51"/>
-      <c r="H43" s="293" t="s">
+      <c r="H43" s="253" t="s">
         <v>60</v>
       </c>
-      <c r="I43" s="294"/>
-      <c r="J43" s="294"/>
+      <c r="I43" s="275"/>
+      <c r="J43" s="275"/>
       <c r="K43" s="92">
         <v>300</v>
       </c>
@@ -16885,14 +16879,14 @@
       <c r="B44" s="42"/>
       <c r="C44" s="42"/>
       <c r="D44" s="51"/>
-      <c r="H44" s="222" t="str">
+      <c r="H44" s="293" t="str">
         <f>IF(K43&gt;=J12,'1'!A69,'1'!A70)</f>
         <v>Т.Т. соответствует нагрузке</v>
       </c>
-      <c r="I44" s="223"/>
-      <c r="J44" s="223"/>
-      <c r="K44" s="223"/>
-      <c r="L44" s="223"/>
+      <c r="I44" s="294"/>
+      <c r="J44" s="294"/>
+      <c r="K44" s="294"/>
+      <c r="L44" s="294"/>
       <c r="M44" s="8"/>
     </row>
     <row r="45" spans="1:28" ht="12.75" customHeight="1">
@@ -16906,60 +16900,60 @@
       <c r="H45" s="205"/>
       <c r="I45" s="205"/>
       <c r="J45" s="205"/>
-      <c r="K45" s="236" t="s">
+      <c r="K45" s="305" t="s">
         <v>73</v>
       </c>
-      <c r="L45" s="237"/>
-      <c r="M45" s="309"/>
-      <c r="N45" s="309"/>
-      <c r="O45" s="309"/>
-      <c r="P45" s="309"/>
-      <c r="Q45" s="309"/>
-      <c r="R45" s="309"/>
-      <c r="S45" s="309"/>
-      <c r="T45" s="309"/>
-      <c r="U45" s="309"/>
-      <c r="V45" s="309"/>
-      <c r="W45" s="309"/>
-      <c r="X45" s="309"/>
-      <c r="Y45" s="309"/>
-      <c r="Z45" s="309"/>
-      <c r="AA45" s="309"/>
-      <c r="AB45" s="310"/>
+      <c r="L45" s="306"/>
+      <c r="M45" s="276"/>
+      <c r="N45" s="276"/>
+      <c r="O45" s="276"/>
+      <c r="P45" s="276"/>
+      <c r="Q45" s="276"/>
+      <c r="R45" s="276"/>
+      <c r="S45" s="276"/>
+      <c r="T45" s="276"/>
+      <c r="U45" s="276"/>
+      <c r="V45" s="276"/>
+      <c r="W45" s="276"/>
+      <c r="X45" s="276"/>
+      <c r="Y45" s="276"/>
+      <c r="Z45" s="276"/>
+      <c r="AA45" s="276"/>
+      <c r="AB45" s="277"/>
     </row>
     <row r="46" spans="1:28" ht="23.25" customHeight="1">
-      <c r="A46" s="268" t="s">
+      <c r="A46" s="288" t="s">
         <v>74</v>
       </c>
-      <c r="B46" s="269"/>
+      <c r="B46" s="289"/>
       <c r="C46" s="200"/>
-      <c r="D46" s="270" t="s">
+      <c r="D46" s="290" t="s">
         <v>71</v>
       </c>
-      <c r="E46" s="270"/>
-      <c r="F46" s="270"/>
+      <c r="E46" s="290"/>
+      <c r="F46" s="290"/>
       <c r="G46" s="201"/>
       <c r="H46" s="70"/>
       <c r="I46" s="70"/>
       <c r="J46" s="199"/>
-      <c r="K46" s="238"/>
-      <c r="L46" s="239"/>
-      <c r="M46" s="311"/>
-      <c r="N46" s="311"/>
-      <c r="O46" s="311"/>
-      <c r="P46" s="311"/>
-      <c r="Q46" s="311"/>
-      <c r="R46" s="311"/>
-      <c r="S46" s="311"/>
-      <c r="T46" s="311"/>
-      <c r="U46" s="311"/>
-      <c r="V46" s="311"/>
-      <c r="W46" s="311"/>
-      <c r="X46" s="311"/>
-      <c r="Y46" s="311"/>
-      <c r="Z46" s="311"/>
-      <c r="AA46" s="311"/>
-      <c r="AB46" s="312"/>
+      <c r="K46" s="307"/>
+      <c r="L46" s="308"/>
+      <c r="M46" s="278"/>
+      <c r="N46" s="278"/>
+      <c r="O46" s="278"/>
+      <c r="P46" s="278"/>
+      <c r="Q46" s="278"/>
+      <c r="R46" s="278"/>
+      <c r="S46" s="278"/>
+      <c r="T46" s="278"/>
+      <c r="U46" s="278"/>
+      <c r="V46" s="278"/>
+      <c r="W46" s="278"/>
+      <c r="X46" s="278"/>
+      <c r="Y46" s="278"/>
+      <c r="Z46" s="278"/>
+      <c r="AA46" s="278"/>
+      <c r="AB46" s="279"/>
     </row>
     <row r="47" spans="1:28" ht="21" customHeight="1">
       <c r="A47" s="62"/>
@@ -16967,105 +16961,105 @@
         <v>2</v>
       </c>
       <c r="C47" s="199"/>
-      <c r="D47" s="227">
+      <c r="D47" s="298">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
-      </c>
-      <c r="E47" s="227"/>
-      <c r="F47" s="227"/>
-      <c r="G47" s="227"/>
-      <c r="H47" s="277" t="s">
+        <v>46117</v>
+      </c>
+      <c r="E47" s="298"/>
+      <c r="F47" s="298"/>
+      <c r="G47" s="298"/>
+      <c r="H47" s="265" t="s">
         <v>76</v>
       </c>
-      <c r="I47" s="277"/>
-      <c r="J47" s="277"/>
+      <c r="I47" s="265"/>
+      <c r="J47" s="265"/>
       <c r="K47" s="7"/>
-      <c r="M47" s="311"/>
-      <c r="N47" s="311"/>
-      <c r="O47" s="311"/>
-      <c r="P47" s="311"/>
-      <c r="Q47" s="311"/>
-      <c r="R47" s="311"/>
-      <c r="S47" s="311"/>
-      <c r="T47" s="311"/>
-      <c r="U47" s="311"/>
-      <c r="V47" s="311"/>
-      <c r="W47" s="311"/>
-      <c r="X47" s="311"/>
-      <c r="Y47" s="311"/>
-      <c r="Z47" s="311"/>
-      <c r="AA47" s="311"/>
-      <c r="AB47" s="312"/>
+      <c r="M47" s="278"/>
+      <c r="N47" s="278"/>
+      <c r="O47" s="278"/>
+      <c r="P47" s="278"/>
+      <c r="Q47" s="278"/>
+      <c r="R47" s="278"/>
+      <c r="S47" s="278"/>
+      <c r="T47" s="278"/>
+      <c r="U47" s="278"/>
+      <c r="V47" s="278"/>
+      <c r="W47" s="278"/>
+      <c r="X47" s="278"/>
+      <c r="Y47" s="278"/>
+      <c r="Z47" s="278"/>
+      <c r="AA47" s="278"/>
+      <c r="AB47" s="279"/>
     </row>
     <row r="48" spans="1:28" ht="21" customHeight="1" thickBot="1">
       <c r="A48" s="63"/>
       <c r="B48" s="64"/>
       <c r="C48" s="64"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
-      <c r="G48" s="228"/>
-      <c r="H48" s="278"/>
-      <c r="I48" s="278"/>
-      <c r="J48" s="278"/>
+      <c r="D48" s="299"/>
+      <c r="E48" s="299"/>
+      <c r="F48" s="299"/>
+      <c r="G48" s="299"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
       <c r="K48" s="7"/>
-      <c r="M48" s="311"/>
-      <c r="N48" s="311"/>
-      <c r="O48" s="311"/>
-      <c r="P48" s="311"/>
-      <c r="Q48" s="311"/>
-      <c r="R48" s="311"/>
-      <c r="S48" s="311"/>
-      <c r="T48" s="311"/>
-      <c r="U48" s="311"/>
-      <c r="V48" s="311"/>
-      <c r="W48" s="311"/>
-      <c r="X48" s="311"/>
-      <c r="Y48" s="311"/>
-      <c r="Z48" s="311"/>
-      <c r="AA48" s="311"/>
-      <c r="AB48" s="312"/>
+      <c r="M48" s="278"/>
+      <c r="N48" s="278"/>
+      <c r="O48" s="278"/>
+      <c r="P48" s="278"/>
+      <c r="Q48" s="278"/>
+      <c r="R48" s="278"/>
+      <c r="S48" s="278"/>
+      <c r="T48" s="278"/>
+      <c r="U48" s="278"/>
+      <c r="V48" s="278"/>
+      <c r="W48" s="278"/>
+      <c r="X48" s="278"/>
+      <c r="Y48" s="278"/>
+      <c r="Z48" s="278"/>
+      <c r="AA48" s="278"/>
+      <c r="AB48" s="279"/>
     </row>
     <row r="49" spans="1:28" ht="21" customHeight="1">
-      <c r="A49" s="260" t="s">
+      <c r="A49" s="280" t="s">
         <v>155</v>
       </c>
-      <c r="B49" s="264" t="s">
+      <c r="B49" s="284" t="s">
         <v>152</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="282" t="s">
         <v>72</v>
       </c>
-      <c r="D49" s="288">
+      <c r="D49" s="270">
         <v>46085</v>
       </c>
-      <c r="E49" s="288"/>
-      <c r="F49" s="288"/>
-      <c r="G49" s="288"/>
-      <c r="H49" s="288"/>
-      <c r="I49" s="288"/>
-      <c r="J49" s="288"/>
+      <c r="E49" s="270"/>
+      <c r="F49" s="270"/>
+      <c r="G49" s="270"/>
+      <c r="H49" s="270"/>
+      <c r="I49" s="270"/>
+      <c r="J49" s="270"/>
       <c r="K49" s="7"/>
-      <c r="W49" s="271" t="s">
+      <c r="W49" s="259" t="s">
         <v>147</v>
       </c>
-      <c r="X49" s="272"/>
-      <c r="Y49" s="272"/>
-      <c r="Z49" s="272"/>
-      <c r="AA49" s="272"/>
-      <c r="AB49" s="273"/>
+      <c r="X49" s="260"/>
+      <c r="Y49" s="260"/>
+      <c r="Z49" s="260"/>
+      <c r="AA49" s="260"/>
+      <c r="AB49" s="261"/>
     </row>
     <row r="50" spans="1:28" ht="21" customHeight="1" thickBot="1">
-      <c r="A50" s="261"/>
-      <c r="B50" s="265"/>
-      <c r="C50" s="263"/>
-      <c r="D50" s="289"/>
-      <c r="E50" s="289"/>
-      <c r="F50" s="289"/>
-      <c r="G50" s="289"/>
-      <c r="H50" s="289"/>
-      <c r="I50" s="289"/>
-      <c r="J50" s="289"/>
+      <c r="A50" s="281"/>
+      <c r="B50" s="285"/>
+      <c r="C50" s="283"/>
+      <c r="D50" s="271"/>
+      <c r="E50" s="271"/>
+      <c r="F50" s="271"/>
+      <c r="G50" s="271"/>
+      <c r="H50" s="271"/>
+      <c r="I50" s="271"/>
+      <c r="J50" s="271"/>
       <c r="K50" s="65"/>
       <c r="L50" s="9"/>
       <c r="M50" s="9"/>
@@ -17078,15 +17072,55 @@
       <c r="T50" s="9"/>
       <c r="U50" s="9"/>
       <c r="V50" s="9"/>
-      <c r="W50" s="274"/>
-      <c r="X50" s="275"/>
-      <c r="Y50" s="275"/>
-      <c r="Z50" s="275"/>
-      <c r="AA50" s="275"/>
-      <c r="AB50" s="276"/>
+      <c r="W50" s="262"/>
+      <c r="X50" s="263"/>
+      <c r="Y50" s="263"/>
+      <c r="Z50" s="263"/>
+      <c r="AA50" s="263"/>
+      <c r="AB50" s="264"/>
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="L14:L18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H44:L44"/>
+    <mergeCell ref="H35:J36"/>
+    <mergeCell ref="D47:G48"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="K45:L46"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="H14:K15"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="A22:D24"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H4:H12"/>
+    <mergeCell ref="W49:AB50"/>
+    <mergeCell ref="H47:J48"/>
+    <mergeCell ref="L35:L36"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="H29:M30"/>
+    <mergeCell ref="D49:J50"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="M45:AB48"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="H1:AB3"/>
@@ -17103,46 +17137,6 @@
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H4:H12"/>
-    <mergeCell ref="W49:AB50"/>
-    <mergeCell ref="H47:J48"/>
-    <mergeCell ref="L35:L36"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="H29:M30"/>
-    <mergeCell ref="D49:J50"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="M45:AB48"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="L14:L18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H44:L44"/>
-    <mergeCell ref="H35:J36"/>
-    <mergeCell ref="D47:G48"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="K45:L46"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="H14:K15"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="A22:D24"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.43307086614173229" top="0.82677165354330717" bottom="0" header="0.51181102362204722" footer="0"/>
@@ -17844,7 +17838,7 @@
       <c r="H16" s="107"/>
       <c r="I16" s="112">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75">
@@ -17860,7 +17854,7 @@
       <c r="H17" s="107"/>
       <c r="I17" s="117">
         <f>Расчет!K26/Расчет!K43*5</f>
-        <v>16.333333333333332</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75">
@@ -17932,7 +17926,7 @@
       <c r="H22" s="107"/>
       <c r="I22" s="112">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75">
@@ -17948,7 +17942,7 @@
       <c r="H23" s="107"/>
       <c r="I23" s="117">
         <f>Расчет!K33/Расчет!K43*5</f>
-        <v>1.2466666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75">
@@ -18524,7 +18518,7 @@
       </c>
       <c r="H8" s="7"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="333" t="b">
+      <c r="M8" s="331" t="b">
         <f>IF(L9+L11+L13+L15=B9,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -18537,7 +18531,7 @@
       </c>
       <c r="B9" s="32">
         <f>0.1*Расчет!D20</f>
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>2</v>
@@ -18547,21 +18541,21 @@
       </c>
       <c r="I9">
         <f>IF(Расчет!D9+Расчет!D10&gt;=B9,B9,K9)</f>
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J9">
         <f>IF(Расчет!D9+Расчет!D10=B9,B9,K9)</f>
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="K9">
         <f>IF(Расчет!D9+Расчет!D10&lt;B9,Расчет!D9+Расчет!D10,I9)</f>
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="L9" s="15">
         <f>IF(K9&lt;=0,0,K9)</f>
-        <v>5.2</v>
-      </c>
-      <c r="M9" s="333"/>
+        <v>0.8</v>
+      </c>
+      <c r="M9" s="331"/>
       <c r="N9" s="24"/>
       <c r="R9" s="41"/>
       <c r="W9" s="152"/>
@@ -18572,14 +18566,14 @@
       </c>
       <c r="B10" s="32">
         <f>0.2*Расчет!D20</f>
-        <v>10.4</v>
+        <v>1.6</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H10" s="7"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="333"/>
+      <c r="M10" s="331"/>
       <c r="N10" s="24"/>
       <c r="W10" s="152"/>
     </row>
@@ -18589,7 +18583,7 @@
       </c>
       <c r="B11" s="32">
         <f>0.3*Расчет!D20</f>
-        <v>15.6</v>
+        <v>2.4</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>2</v>
@@ -18607,13 +18601,13 @@
       </c>
       <c r="K11">
         <f>IF(B9&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,Расчет!D12+Расчет!D13,B9-(Расчет!D9+Расчет!D10))</f>
-        <v>-19.8</v>
+        <v>-1.2</v>
       </c>
       <c r="L11" s="15">
         <f>IF(K11&lt;=0,0,K11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="333"/>
+      <c r="M11" s="331"/>
       <c r="N11" s="24"/>
       <c r="R11" s="41"/>
       <c r="W11" s="152"/>
@@ -18624,14 +18618,14 @@
       </c>
       <c r="B12" s="32">
         <f>0.4*Расчет!D20</f>
-        <v>20.8</v>
+        <v>3.2</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H12" s="7"/>
       <c r="L12" s="3"/>
-      <c r="M12" s="333"/>
+      <c r="M12" s="331"/>
       <c r="N12" s="24"/>
       <c r="W12" s="152"/>
     </row>
@@ -18641,7 +18635,7 @@
       </c>
       <c r="B13" s="32">
         <f>0.5*Расчет!D20</f>
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>2</v>
@@ -18659,13 +18653,13 @@
       </c>
       <c r="K13">
         <f>IF(B9&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,Расчет!D15+Расчет!D16,B9-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13))</f>
-        <v>-24.8</v>
+        <v>-3.2</v>
       </c>
       <c r="L13" s="15">
         <f>IF(K13&lt;=0,0,K13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="333"/>
+      <c r="M13" s="331"/>
       <c r="N13" s="24"/>
       <c r="R13" s="41"/>
       <c r="W13" s="152"/>
@@ -18676,14 +18670,14 @@
       </c>
       <c r="B14" s="32">
         <f>0.6*Расчет!D20</f>
-        <v>31.2</v>
+        <v>4.8</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H14" s="7"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="333"/>
+      <c r="M14" s="331"/>
       <c r="N14" s="24"/>
       <c r="W14" s="152"/>
     </row>
@@ -18693,7 +18687,7 @@
       </c>
       <c r="B15" s="32">
         <f>0.7*Расчет!D20</f>
-        <v>36.4</v>
+        <v>5.6</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>2</v>
@@ -18711,13 +18705,13 @@
       </c>
       <c r="K15" s="9">
         <f>IF(B9&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16+Расчет!D18+Расчет!D19,Расчет!D18+Расчет!D19,B9-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16))</f>
-        <v>-33.799999999999997</v>
+        <v>-5.2</v>
       </c>
       <c r="L15" s="162">
         <f>IF(K15&lt;=0,0,K15)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="334"/>
+      <c r="M15" s="340"/>
       <c r="N15" s="24"/>
       <c r="R15" s="41"/>
       <c r="W15" s="152"/>
@@ -18728,7 +18722,7 @@
       </c>
       <c r="B16" s="32">
         <f>0.8*Расчет!D20</f>
-        <v>41.6</v>
+        <v>6.4</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>2</v>
@@ -18741,7 +18735,7 @@
       </c>
       <c r="J16" s="159">
         <f>SQRT((SUMSQ(L9*(Расчет!E9+Расчет!E10)+L11*(Расчет!E12+Расчет!E13)+L13*(Расчет!E15+Расчет!E16)+L15*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F5+L9*(Расчет!F9+Расчет!F10)+L11*(Расчет!F12+Расчет!F13)+L13*(Расчет!F15+Расчет!F16)+L15*(Расчет!F18+Расчет!F19))))</f>
-        <v>3.0142487613923898</v>
+        <v>3.5315652337171972</v>
       </c>
       <c r="K16" s="160" t="s">
         <v>141</v>
@@ -18761,7 +18755,7 @@
       </c>
       <c r="B17" s="32">
         <f>0.9*Расчет!D20</f>
-        <v>46.800000000000004</v>
+        <v>7.2</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>2</v>
@@ -18781,7 +18775,7 @@
       </c>
       <c r="B18" s="33">
         <f>1*Расчет!D20</f>
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>2</v>
@@ -18805,13 +18799,13 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="27"/>
-      <c r="D19" s="335" t="s">
+      <c r="D19" s="341" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="332"/>
+      <c r="E19" s="339"/>
       <c r="H19" s="7"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="333" t="b">
+      <c r="M19" s="331" t="b">
         <f>IF(L20+L22+L24+L26=B10,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -18820,10 +18814,10 @@
       </c>
       <c r="P19" s="26"/>
       <c r="Q19" s="27"/>
-      <c r="R19" s="331" t="s">
+      <c r="R19" s="338" t="s">
         <v>35</v>
       </c>
-      <c r="S19" s="332"/>
+      <c r="S19" s="339"/>
     </row>
     <row r="20" spans="1:19" ht="13.5" thickBot="1">
       <c r="A20" s="30" t="s">
@@ -18848,21 +18842,21 @@
       </c>
       <c r="I20">
         <f>IF(Расчет!D9+Расчет!D10&gt;=B10,B10,K20)</f>
-        <v>10.4</v>
+        <v>1.6</v>
       </c>
       <c r="J20">
         <f>IF(Расчет!D9+Расчет!D10=B10,B10,K20)</f>
-        <v>10.4</v>
+        <v>1.6</v>
       </c>
       <c r="K20">
         <f>IF(Расчет!D9+Расчет!D10&lt;B10,Расчет!D9+Расчет!D10,I20)</f>
-        <v>10.4</v>
+        <v>1.6</v>
       </c>
       <c r="L20" s="15">
         <f>IF(K20&lt;=0,0,K20)</f>
-        <v>10.4</v>
-      </c>
-      <c r="M20" s="333"/>
+        <v>1.6</v>
+      </c>
+      <c r="M20" s="331"/>
       <c r="O20" s="30" t="s">
         <v>32</v>
       </c>
@@ -18887,21 +18881,21 @@
       </c>
       <c r="B21" s="32">
         <f>6300/(2*J16)</f>
-        <v>1045.0365080501524</v>
+        <v>891.95577358326875</v>
       </c>
       <c r="C21" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="15">
         <f t="shared" si="0"/>
-        <v>696.69100536676831</v>
+        <v>594.63718238884587</v>
       </c>
       <c r="E21" s="45" t="s">
         <v>31</v>
       </c>
       <c r="H21" s="7"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="333"/>
+      <c r="M21" s="331"/>
       <c r="O21" s="30" t="s">
         <v>7</v>
       </c>
@@ -18926,14 +18920,14 @@
       </c>
       <c r="B22" s="32">
         <f>6300/(2*J27)</f>
-        <v>572.74645249158289</v>
+        <v>454.86457853061512</v>
       </c>
       <c r="C22" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="48">
         <f t="shared" si="0"/>
-        <v>381.83096832772191</v>
+        <v>303.24305235374339</v>
       </c>
       <c r="E22" s="45" t="s">
         <v>31</v>
@@ -18951,13 +18945,13 @@
       </c>
       <c r="K22">
         <f>IF(B10&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,Расчет!D12+Расчет!D13,B10-(Расчет!D9+Расчет!D10))</f>
-        <v>-14.6</v>
+        <v>-0.39999999999999991</v>
       </c>
       <c r="L22" s="15">
         <f>IF(K22&lt;=0,0,K22)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="333"/>
+      <c r="M22" s="331"/>
       <c r="O22" s="30" t="s">
         <v>8</v>
       </c>
@@ -18982,21 +18976,21 @@
       </c>
       <c r="B23" s="32">
         <f>6300/(2*J38)</f>
-        <v>394.31272734370668</v>
+        <v>304.82500824396641</v>
       </c>
       <c r="C23" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="48">
         <f t="shared" si="0"/>
-        <v>262.8751515624711</v>
+        <v>203.21667216264427</v>
       </c>
       <c r="E23" s="45" t="s">
         <v>31</v>
       </c>
       <c r="H23" s="7"/>
       <c r="L23" s="3"/>
-      <c r="M23" s="333"/>
+      <c r="M23" s="331"/>
       <c r="O23" s="30" t="s">
         <v>9</v>
       </c>
@@ -19021,14 +19015,14 @@
       </c>
       <c r="B24" s="32">
         <f>6300/(2*J49)</f>
-        <v>300.62212779780572</v>
+        <v>229.15214187618625</v>
       </c>
       <c r="C24" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D24" s="48">
         <f t="shared" si="0"/>
-        <v>200.41475186520381</v>
+        <v>152.76809458412416</v>
       </c>
       <c r="E24" s="45" t="s">
         <v>31</v>
@@ -19046,13 +19040,13 @@
       </c>
       <c r="K24">
         <f>IF(B10&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,Расчет!D15+Расчет!D16,B10-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13))</f>
-        <v>-19.600000000000001</v>
+        <v>-2.4</v>
       </c>
       <c r="L24" s="15">
         <f>IF(K24&lt;=0,0,K24)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="333"/>
+      <c r="M24" s="331"/>
       <c r="O24" s="30" t="s">
         <v>10</v>
       </c>
@@ -19077,21 +19071,21 @@
       </c>
       <c r="B25" s="32">
         <f>6300/(2*J60)</f>
-        <v>243.05643506948761</v>
+        <v>183.56199987721141</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D25" s="48">
         <f t="shared" si="0"/>
-        <v>162.03762337965841</v>
+        <v>122.3746665848076</v>
       </c>
       <c r="E25" s="45" t="s">
         <v>31</v>
       </c>
       <c r="H25" s="7"/>
       <c r="L25" s="3"/>
-      <c r="M25" s="333"/>
+      <c r="M25" s="331"/>
       <c r="O25" s="30" t="s">
         <v>11</v>
       </c>
@@ -19116,14 +19110,14 @@
       </c>
       <c r="B26" s="32">
         <f>6300/(2*J71)</f>
-        <v>204.45822779421155</v>
+        <v>153.09628526363929</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D26" s="48">
         <f t="shared" si="0"/>
-        <v>136.30548519614103</v>
+        <v>102.06419017575952</v>
       </c>
       <c r="E26" s="45" t="s">
         <v>31</v>
@@ -19141,13 +19135,13 @@
       </c>
       <c r="K26">
         <f>IF(B10&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16+Расчет!D18+Расчет!D19,Расчет!D18+Расчет!D19,B10-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16))</f>
-        <v>-28.6</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="L26" s="15">
         <f>IF(K26&lt;=0,0,K26)</f>
         <v>0</v>
       </c>
-      <c r="M26" s="333"/>
+      <c r="M26" s="331"/>
       <c r="O26" s="30" t="s">
         <v>12</v>
       </c>
@@ -19172,14 +19166,14 @@
       </c>
       <c r="B27" s="32">
         <f>6300/(2*J82)</f>
-        <v>176.43800569026689</v>
+        <v>131.30137977998902</v>
       </c>
       <c r="C27" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D27" s="48">
         <f t="shared" si="0"/>
-        <v>117.6253371268446</v>
+        <v>87.534253186659342</v>
       </c>
       <c r="E27" s="45" t="s">
         <v>31</v>
@@ -19192,7 +19186,7 @@
       </c>
       <c r="J27" s="25">
         <f>SQRT((SUMSQ(L20*(Расчет!E9+Расчет!E10)+L22*(Расчет!E12+Расчет!E13)+L24*(Расчет!E15+Расчет!E16)+L26*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F5+L20*(Расчет!F9+Расчет!F10)+L22*(Расчет!F12+Расчет!F13)+L24*(Расчет!F15+Расчет!F16)+L26*(Расчет!F18+Расчет!F19))))</f>
-        <v>5.4998158195424054</v>
+        <v>6.9251380491655192</v>
       </c>
       <c r="K27" s="160" t="s">
         <v>141</v>
@@ -19223,14 +19217,14 @@
       </c>
       <c r="B28" s="32">
         <f>6300/(2*J93)</f>
-        <v>151.91819160635805</v>
+        <v>114.93744856736167</v>
       </c>
       <c r="C28" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D28" s="48">
         <f t="shared" si="0"/>
-        <v>101.2787944042387</v>
+        <v>76.624965711574447</v>
       </c>
       <c r="E28" s="45" t="s">
         <v>31</v>
@@ -19266,14 +19260,14 @@
       </c>
       <c r="B29" s="32">
         <f>6300/(2*J104)</f>
-        <v>129.71875066013595</v>
+        <v>102.19972160433029</v>
       </c>
       <c r="C29" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D29" s="48">
         <f t="shared" si="0"/>
-        <v>86.479167106757302</v>
+        <v>68.133147736220195</v>
       </c>
       <c r="E29" s="45" t="s">
         <v>31</v>
@@ -19314,21 +19308,21 @@
       </c>
       <c r="B30" s="33">
         <f>6300/(2*J115)</f>
-        <v>112.32956325113049</v>
+        <v>92.003242367296878</v>
       </c>
       <c r="C30" s="35" t="s">
         <v>31</v>
       </c>
       <c r="D30" s="49">
         <f t="shared" si="0"/>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="E30" s="46" t="s">
         <v>31</v>
       </c>
       <c r="H30" s="7"/>
       <c r="L30" s="7"/>
-      <c r="M30" s="333" t="b">
+      <c r="M30" s="331" t="b">
         <f>IF(L31+L33+L35+L37=B11,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -19356,7 +19350,7 @@
       </c>
       <c r="B31" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C31" s="39" t="s">
         <v>31</v>
@@ -19366,21 +19360,21 @@
       </c>
       <c r="I31">
         <f>IF(Расчет!D9+Расчет!D10&gt;=B11,B11,K31)</f>
-        <v>15.6</v>
+        <v>2</v>
       </c>
       <c r="J31">
         <f>IF(Расчет!D9+Расчет!D10=B11,B11,K31)</f>
-        <v>15.6</v>
+        <v>2</v>
       </c>
       <c r="K31">
         <f>IF(Расчет!D9+Расчет!D10&lt;B11,Расчет!D9+Расчет!D10,I31)</f>
-        <v>15.6</v>
+        <v>2</v>
       </c>
       <c r="L31" s="15">
         <f>IF(K31&lt;=0,0,K31)</f>
-        <v>15.6</v>
-      </c>
-      <c r="M31" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M31" s="331"/>
       <c r="O31" s="38" t="s">
         <v>33</v>
       </c>
@@ -19398,14 +19392,14 @@
       </c>
       <c r="B32" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C32" s="39" t="s">
         <v>31</v>
       </c>
       <c r="H32" s="7"/>
       <c r="L32" s="7"/>
-      <c r="M32" s="333"/>
+      <c r="M32" s="331"/>
       <c r="O32" s="38" t="s">
         <v>33</v>
       </c>
@@ -19423,7 +19417,7 @@
       </c>
       <c r="B33" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C33" s="39" t="s">
         <v>31</v>
@@ -19433,21 +19427,21 @@
       </c>
       <c r="I33">
         <f>IF(Расчет!D12+Расчет!D13&lt;=0,0,J33)</f>
-        <v>0</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="J33">
         <f>IF(B11&lt;=Расчет!D9+Расчет!D10,0,K33)</f>
-        <v>0</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="K33">
         <f>IF(B11&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,Расчет!D12+Расчет!D13,B11-(Расчет!D9+Расчет!D10))</f>
-        <v>-9.4</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="L33" s="15">
         <f>IF(K33&lt;=0,0,K33)</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="333"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="M33" s="331"/>
       <c r="O33" s="38" t="s">
         <v>33</v>
       </c>
@@ -19465,14 +19459,14 @@
       </c>
       <c r="B34" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C34" s="39" t="s">
         <v>31</v>
       </c>
       <c r="H34" s="7"/>
       <c r="L34" s="7"/>
-      <c r="M34" s="333"/>
+      <c r="M34" s="331"/>
       <c r="O34" s="38" t="s">
         <v>33</v>
       </c>
@@ -19490,7 +19484,7 @@
       </c>
       <c r="B35" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C35" s="39" t="s">
         <v>31</v>
@@ -19508,13 +19502,13 @@
       </c>
       <c r="K35">
         <f>IF(B11&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,Расчет!D15+Расчет!D16,B11-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13))</f>
-        <v>-14.4</v>
+        <v>-1.6</v>
       </c>
       <c r="L35" s="15">
         <f>IF(K35&lt;=0,0,K35)</f>
         <v>0</v>
       </c>
-      <c r="M35" s="333"/>
+      <c r="M35" s="331"/>
       <c r="O35" s="38" t="s">
         <v>33</v>
       </c>
@@ -19532,14 +19526,14 @@
       </c>
       <c r="B36" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C36" s="39" t="s">
         <v>31</v>
       </c>
       <c r="H36" s="7"/>
       <c r="L36" s="7"/>
-      <c r="M36" s="333"/>
+      <c r="M36" s="331"/>
       <c r="O36" s="38" t="s">
         <v>33</v>
       </c>
@@ -19557,7 +19551,7 @@
       </c>
       <c r="B37" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C37" s="39" t="s">
         <v>31</v>
@@ -19575,13 +19569,13 @@
       </c>
       <c r="K37">
         <f>IF(B11&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16+Расчет!D18+Расчет!D19,Расчет!D18+Расчет!D19,B11-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16))</f>
-        <v>-23.4</v>
+        <v>-3.6</v>
       </c>
       <c r="L37" s="15">
         <f>IF(K37&lt;=0,0,K37)</f>
         <v>0</v>
       </c>
-      <c r="M37" s="333"/>
+      <c r="M37" s="331"/>
       <c r="O37" s="38" t="s">
         <v>33</v>
       </c>
@@ -19599,7 +19593,7 @@
       </c>
       <c r="B38" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C38" s="39" t="s">
         <v>31</v>
@@ -19612,7 +19606,7 @@
       </c>
       <c r="J38" s="25">
         <f>SQRT((SUMSQ(L31*(Расчет!E9+Расчет!E10)+L33*(Расчет!E12+Расчет!E13)+L35*(Расчет!E15+Расчет!E16)+L37*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F5+L31*(Расчет!F9+Расчет!F10)+L33*(Расчет!F12+Расчет!F13)+L35*(Расчет!F15+Расчет!F16)+L37*(Расчет!F18+Расчет!F19))))</f>
-        <v>7.9885831259366649</v>
+        <v>10.33379780138938</v>
       </c>
       <c r="K38" s="160" t="s">
         <v>141</v>
@@ -19636,7 +19630,7 @@
       </c>
       <c r="B39" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C39" s="39" t="s">
         <v>31</v>
@@ -19665,7 +19659,7 @@
       </c>
       <c r="B40" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C40" s="39" t="s">
         <v>31</v>
@@ -19699,14 +19693,14 @@
       </c>
       <c r="B41" s="36">
         <f>B30/1.5</f>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="C41" s="39" t="s">
         <v>31</v>
       </c>
       <c r="H41" s="7"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="333" t="b">
+      <c r="M41" s="331" t="b">
         <f>IF(L42+L44+L46+L48=B12,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -19729,21 +19723,21 @@
       </c>
       <c r="I42">
         <f>IF(Расчет!D9+Расчет!D10&gt;=B12,B12,K42)</f>
-        <v>20.8</v>
+        <v>2</v>
       </c>
       <c r="J42">
         <f>IF(Расчет!D9+Расчет!D10=B12,B12,K42)</f>
-        <v>20.8</v>
+        <v>2</v>
       </c>
       <c r="K42">
         <f>IF(Расчет!D9+Расчет!D10&lt;B12,Расчет!D9+Расчет!D10,I42)</f>
-        <v>20.8</v>
+        <v>2</v>
       </c>
       <c r="L42" s="15">
         <f>IF(K42&lt;=0,0,K42)</f>
-        <v>20.8</v>
-      </c>
-      <c r="M42" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M42" s="331"/>
     </row>
     <row r="43" spans="1:17" ht="13.5" thickBot="1">
       <c r="A43" s="28" t="s">
@@ -19755,7 +19749,7 @@
       <c r="E43" s="42"/>
       <c r="H43" s="7"/>
       <c r="L43" s="3"/>
-      <c r="M43" s="333"/>
+      <c r="M43" s="331"/>
       <c r="O43" s="28" t="s">
         <v>47</v>
       </c>
@@ -19768,7 +19762,7 @@
       </c>
       <c r="B44" s="187">
         <f>IFERROR(6300/(SQRT(3)*J118),"---")</f>
-        <v>229.97054311746939</v>
+        <v>98.61123989226688</v>
       </c>
       <c r="C44" s="46" t="s">
         <v>31</v>
@@ -19778,21 +19772,21 @@
       </c>
       <c r="I44">
         <f>IF(Расчет!D12+Расчет!D13&lt;=0,0,J44)</f>
-        <v>0</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J44">
         <f>IF(B12&lt;=Расчет!D9+Расчет!D10,0,K44)</f>
-        <v>0</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="K44">
         <f>IF(B12&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,Расчет!D12+Расчет!D13,B12-(Расчет!D9+Расчет!D10))</f>
-        <v>-4.1999999999999993</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="L44" s="15">
         <f>IF(K44&lt;=0,0,K44)</f>
-        <v>0</v>
-      </c>
-      <c r="M44" s="333"/>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="M44" s="331"/>
       <c r="O44" s="50" t="s">
         <v>48</v>
       </c>
@@ -19810,14 +19804,14 @@
       </c>
       <c r="B45" s="1">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C45" s="46" t="s">
         <v>31</v>
       </c>
       <c r="H45" s="7"/>
       <c r="L45" s="3"/>
-      <c r="M45" s="333"/>
+      <c r="M45" s="331"/>
       <c r="O45" s="37" t="s">
         <v>42</v>
       </c>
@@ -19835,7 +19829,7 @@
       </c>
       <c r="B46" s="3">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C46" s="46" t="s">
         <v>31</v>
@@ -19853,13 +19847,13 @@
       </c>
       <c r="K46">
         <f>IF(B12&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,Расчет!D15+Расчет!D16,B12-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13))</f>
-        <v>-9.1999999999999993</v>
+        <v>-0.79999999999999982</v>
       </c>
       <c r="L46" s="15">
         <f>IF(K46&lt;=0,0,K46)</f>
         <v>0</v>
       </c>
-      <c r="M46" s="333"/>
+      <c r="M46" s="331"/>
       <c r="O46" s="54" t="s">
         <v>42</v>
       </c>
@@ -19877,14 +19871,14 @@
       </c>
       <c r="B47" s="3">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C47" s="46" t="s">
         <v>31</v>
       </c>
       <c r="H47" s="7"/>
       <c r="L47" s="3"/>
-      <c r="M47" s="333"/>
+      <c r="M47" s="331"/>
       <c r="O47" s="54" t="s">
         <v>42</v>
       </c>
@@ -19902,7 +19896,7 @@
       </c>
       <c r="B48" s="3">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C48" s="46" t="s">
         <v>31</v>
@@ -19920,13 +19914,13 @@
       </c>
       <c r="K48">
         <f>IF(B12&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16+Расчет!D18+Расчет!D19,Расчет!D18+Расчет!D19,B12-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16))</f>
-        <v>-18.2</v>
+        <v>-2.8</v>
       </c>
       <c r="L48" s="15">
         <f>IF(K48&lt;=0,0,K48)</f>
         <v>0</v>
       </c>
-      <c r="M48" s="333"/>
+      <c r="M48" s="331"/>
       <c r="O48" s="54" t="s">
         <v>42</v>
       </c>
@@ -19944,7 +19938,7 @@
       </c>
       <c r="B49" s="3">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C49" s="46" t="s">
         <v>31</v>
@@ -19957,7 +19951,7 @@
       </c>
       <c r="J49" s="25">
         <f>SQRT((SUMSQ(L42*(Расчет!E9+Расчет!E10)+L44*(Расчет!E12+Расчет!E13)+L46*(Расчет!E15+Расчет!E16)+L48*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F5+L42*(Расчет!F9+Расчет!F10)+L44*(Расчет!F12+Расчет!F13)+L46*(Расчет!F15+Расчет!F16)+L48*(Расчет!F18+Расчет!F19))))</f>
-        <v>10.478270588646243</v>
+        <v>13.746325800009254</v>
       </c>
       <c r="K49" s="160" t="s">
         <v>141</v>
@@ -19981,7 +19975,7 @@
       </c>
       <c r="B50" s="3">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C50" s="46" t="s">
         <v>31</v>
@@ -20010,7 +20004,7 @@
       </c>
       <c r="B51" s="3">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C51" s="46" t="s">
         <v>31</v>
@@ -20044,14 +20038,14 @@
       </c>
       <c r="B52" s="3">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C52" s="46" t="s">
         <v>31</v>
       </c>
       <c r="H52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="333" t="b">
+      <c r="M52" s="331" t="b">
         <f>IF(L53+L55+L57+L59=B13,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -20072,7 +20066,7 @@
       </c>
       <c r="B53" s="3">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C53" s="46" t="s">
         <v>31</v>
@@ -20082,21 +20076,21 @@
       </c>
       <c r="I53">
         <f>IF(Расчет!D9+Расчет!D10&gt;=B13,B13,K53)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J53">
         <f>IF(Расчет!D9+Расчет!D10=B13,B13,K53)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K53">
         <f>IF(Расчет!D9+Расчет!D10&lt;B13,Расчет!D9+Расчет!D10,I53)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L53" s="15">
         <f>IF(K53&lt;=0,0,K53)</f>
-        <v>25</v>
-      </c>
-      <c r="M53" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M53" s="331"/>
       <c r="O53" s="54" t="s">
         <v>42</v>
       </c>
@@ -20114,14 +20108,14 @@
       </c>
       <c r="B54" s="3">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C54" s="46" t="s">
         <v>31</v>
       </c>
       <c r="H54" s="7"/>
       <c r="L54" s="7"/>
-      <c r="M54" s="333"/>
+      <c r="M54" s="331"/>
       <c r="O54" s="54" t="s">
         <v>42</v>
       </c>
@@ -20139,7 +20133,7 @@
       </c>
       <c r="B55" s="2">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="C55" s="46" t="s">
         <v>31</v>
@@ -20149,21 +20143,21 @@
       </c>
       <c r="I55">
         <f>IF(Расчет!D12+Расчет!D13&lt;=0,0,J55)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55">
         <f>IF(B13&lt;=Расчет!D9+Расчет!D10,0,K55)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55">
         <f>IF(B13&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,Расчет!D12+Расчет!D13,B13-(Расчет!D9+Расчет!D10))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="15">
         <f>IF(K55&lt;=0,0,K55)</f>
-        <v>1</v>
-      </c>
-      <c r="M55" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M55" s="331"/>
       <c r="O55" s="55" t="s">
         <v>42</v>
       </c>
@@ -20181,7 +20175,7 @@
       <c r="C56" s="6"/>
       <c r="H56" s="7"/>
       <c r="L56" s="7"/>
-      <c r="M56" s="333"/>
+      <c r="M56" s="331"/>
       <c r="O56" s="4"/>
       <c r="P56" s="5"/>
       <c r="Q56" s="6"/>
@@ -20192,7 +20186,7 @@
       </c>
       <c r="B57">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C57" s="45" t="s">
         <v>31</v>
@@ -20210,13 +20204,13 @@
       </c>
       <c r="K57">
         <f>IF(B13&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,Расчет!D15+Расчет!D16,B13-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13))</f>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L57" s="15">
         <f>IF(K57&lt;=0,0,K57)</f>
         <v>0</v>
       </c>
-      <c r="M57" s="333"/>
+      <c r="M57" s="331"/>
       <c r="O57" s="53" t="s">
         <v>49</v>
       </c>
@@ -20234,14 +20228,14 @@
       </c>
       <c r="B58">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C58" s="45" t="s">
         <v>31</v>
       </c>
       <c r="H58" s="7"/>
       <c r="L58" s="7"/>
-      <c r="M58" s="333"/>
+      <c r="M58" s="331"/>
       <c r="O58" s="53" t="s">
         <v>49</v>
       </c>
@@ -20259,7 +20253,7 @@
       </c>
       <c r="B59">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C59" s="45" t="s">
         <v>31</v>
@@ -20277,13 +20271,13 @@
       </c>
       <c r="K59">
         <f>IF(B13&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16+Расчет!D18+Расчет!D19,Расчет!D18+Расчет!D19,B13-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16))</f>
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="L59" s="15">
         <f>IF(K59&lt;=0,0,K59)</f>
         <v>0</v>
       </c>
-      <c r="M59" s="333"/>
+      <c r="M59" s="331"/>
       <c r="O59" s="53" t="s">
         <v>49</v>
       </c>
@@ -20301,7 +20295,7 @@
       </c>
       <c r="B60">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C60" s="45" t="s">
         <v>31</v>
@@ -20314,7 +20308,7 @@
       </c>
       <c r="J60" s="25">
         <f>SQRT((SUMSQ(L53*(Расчет!E9+Расчет!E10)+L55*(Расчет!E12+Расчет!E13)+L57*(Расчет!E15+Расчет!E16)+L59*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F5+L53*(Расчет!F9+Расчет!F10)+L55*(Расчет!F12+Расчет!F13)+L57*(Расчет!F15+Расчет!F16)+L59*(Расчет!F18+Расчет!F19))))</f>
-        <v>12.959953103481682</v>
+        <v>17.160414476346428</v>
       </c>
       <c r="K60" s="160" t="s">
         <v>141</v>
@@ -20338,7 +20332,7 @@
       </c>
       <c r="B61">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C61" s="45" t="s">
         <v>31</v>
@@ -20367,7 +20361,7 @@
       </c>
       <c r="B62">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C62" s="45" t="s">
         <v>31</v>
@@ -20401,14 +20395,14 @@
       </c>
       <c r="B63">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C63" s="45" t="s">
         <v>31</v>
       </c>
       <c r="H63" s="7"/>
       <c r="L63" s="7"/>
-      <c r="M63" s="333" t="b">
+      <c r="M63" s="331" t="b">
         <f>IF(L64+L66+L68+L70=B14,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -20429,7 +20423,7 @@
       </c>
       <c r="B64">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C64" s="45" t="s">
         <v>31</v>
@@ -20439,21 +20433,21 @@
       </c>
       <c r="I64">
         <f>IF(Расчет!D9+Расчет!D10&gt;=B14,B14,K64)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J64">
         <f>IF(Расчет!D9+Расчет!D10=B14,B14,K64)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K64">
         <f>IF(Расчет!D9+Расчет!D10&lt;B14,Расчет!D9+Расчет!D10,I64)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L64" s="15">
         <f>IF(K64&lt;=0,0,K64)</f>
-        <v>25</v>
-      </c>
-      <c r="M64" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M64" s="331"/>
       <c r="O64" s="53" t="s">
         <v>49</v>
       </c>
@@ -20471,14 +20465,14 @@
       </c>
       <c r="B65">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C65" s="45" t="s">
         <v>31</v>
       </c>
       <c r="H65" s="7"/>
       <c r="L65" s="7"/>
-      <c r="M65" s="333"/>
+      <c r="M65" s="331"/>
       <c r="O65" s="53" t="s">
         <v>49</v>
       </c>
@@ -20496,7 +20490,7 @@
       </c>
       <c r="B66">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C66" s="45" t="s">
         <v>31</v>
@@ -20506,21 +20500,21 @@
       </c>
       <c r="I66">
         <f>IF(Расчет!D12+Расчет!D13&lt;=0,0,J66)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J66">
         <f>IF(B14&lt;=Расчет!D9+Расчет!D10,0,K66)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K66">
         <f>IF(B14&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,Расчет!D12+Расчет!D13,B14-(Расчет!D9+Расчет!D10))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L66" s="15">
         <f>IF(K66&lt;=0,0,K66)</f>
-        <v>5</v>
-      </c>
-      <c r="M66" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M66" s="331"/>
       <c r="O66" s="53" t="s">
         <v>49</v>
       </c>
@@ -20538,14 +20532,14 @@
       </c>
       <c r="B67" s="9">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="C67" s="46" t="s">
         <v>31</v>
       </c>
       <c r="H67" s="7"/>
       <c r="L67" s="7"/>
-      <c r="M67" s="333"/>
+      <c r="M67" s="331"/>
       <c r="O67" s="50" t="s">
         <v>49</v>
       </c>
@@ -20565,40 +20559,40 @@
       </c>
       <c r="I68">
         <f>IF(Расчет!D15+Расчет!D16&lt;=0,0,J68)</f>
-        <v>1.1999999999999993</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="J68">
         <f>IF(B14&lt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,0,K68)</f>
-        <v>1.1999999999999993</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="K68">
         <f>IF(B14&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,Расчет!D15+Расчет!D16,B14-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13))</f>
-        <v>1.1999999999999993</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="L68" s="15">
         <f>IF(K68&lt;=0,0,K68)</f>
-        <v>1.1999999999999993</v>
-      </c>
-      <c r="M68" s="333"/>
+        <v>0.79999999999999982</v>
+      </c>
+      <c r="M68" s="331"/>
     </row>
     <row r="69" spans="1:17">
       <c r="A69" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="B69" s="245" t="s">
+      <c r="B69" s="312" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="337"/>
+      <c r="C69" s="333"/>
       <c r="H69" s="7"/>
       <c r="L69" s="7"/>
-      <c r="M69" s="333"/>
+      <c r="M69" s="331"/>
     </row>
     <row r="70" spans="1:17" ht="13.5" thickBot="1">
       <c r="A70" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="B70" s="247"/>
-      <c r="C70" s="338"/>
+      <c r="B70" s="314"/>
+      <c r="C70" s="334"/>
       <c r="H70" s="20">
         <v>4</v>
       </c>
@@ -20612,13 +20606,13 @@
       </c>
       <c r="K70">
         <f>IF(B14&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16+Расчет!D18+Расчет!D19,Расчет!D18+Расчет!D19,B14-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16))</f>
-        <v>-7.8000000000000007</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="L70" s="15">
         <f>IF(K70&lt;=0,0,K70)</f>
         <v>0</v>
       </c>
-      <c r="M70" s="333"/>
+      <c r="M70" s="331"/>
     </row>
     <row r="71" spans="1:17" ht="15" thickBot="1">
       <c r="H71" s="21" t="s">
@@ -20629,7 +20623,7 @@
       </c>
       <c r="J71" s="25">
         <f>SQRT((SUMSQ(L64*(Расчет!E9+Расчет!E10)+L66*(Расчет!E12+Расчет!E13)+L68*(Расчет!E15+Расчет!E16)+L70*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F5+L64*(Расчет!F9+Расчет!F10)+L66*(Расчет!F12+Расчет!F13)+L68*(Расчет!F15+Расчет!F16)+L70*(Расчет!F18+Расчет!F19))))</f>
-        <v>15.40657000690867</v>
+        <v>20.575286948181308</v>
       </c>
       <c r="K71" s="160" t="s">
         <v>141</v>
@@ -20639,10 +20633,10 @@
     </row>
     <row r="72" spans="1:17" ht="15" thickBot="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="293" t="s">
+      <c r="B72" s="253" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="339"/>
+      <c r="C72" s="335"/>
       <c r="J72" s="193" t="str">
         <f>IFERROR(SQRT((SUMSQ(L64*(Расчет!E9+Расчет!E10)+L66*(Расчет!E12+Расчет!E13)+L68*(Расчет!E15+Расчет!E16)+L70*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F6+L64*(Расчет!F9+Расчет!F10)+L66*(Расчет!F12+Расчет!F13)+L68*(Расчет!F15+Расчет!F16)+L70*(Расчет!F18+Расчет!F19)))),"---")</f>
         <v>---</v>
@@ -20653,8 +20647,8 @@
     </row>
     <row r="73" spans="1:17" ht="13.5" thickBot="1">
       <c r="A73" s="3"/>
-      <c r="B73" s="319"/>
-      <c r="C73" s="340"/>
+      <c r="B73" s="254"/>
+      <c r="C73" s="336"/>
       <c r="H73" s="18" t="s">
         <v>23</v>
       </c>
@@ -20670,11 +20664,11 @@
     </row>
     <row r="74" spans="1:17" ht="13.5" customHeight="1" thickBot="1">
       <c r="A74" s="2"/>
-      <c r="B74" s="320"/>
-      <c r="C74" s="341"/>
+      <c r="B74" s="255"/>
+      <c r="C74" s="337"/>
       <c r="H74" s="7"/>
       <c r="L74" s="7"/>
-      <c r="M74" s="333" t="b">
+      <c r="M74" s="331" t="b">
         <f>IF(L75+L77+L79+L81=B15,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -20685,26 +20679,26 @@
       </c>
       <c r="I75">
         <f>IF(Расчет!D9+Расчет!D10&gt;=B15,B15,K75)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J75">
         <f>IF(Расчет!D9+Расчет!D10=B15,B15,K75)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K75">
         <f>IF(Расчет!D9+Расчет!D10&lt;B15,Расчет!D9+Расчет!D10,I75)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L75" s="15">
         <f>IF(K75&lt;=0,0,K75)</f>
-        <v>25</v>
-      </c>
-      <c r="M75" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M75" s="331"/>
     </row>
     <row r="76" spans="1:17">
       <c r="H76" s="7"/>
       <c r="L76" s="7"/>
-      <c r="M76" s="333"/>
+      <c r="M76" s="331"/>
     </row>
     <row r="77" spans="1:17">
       <c r="H77" s="20">
@@ -20712,26 +20706,26 @@
       </c>
       <c r="I77">
         <f>IF(Расчет!D12+Расчет!D13&lt;=0,0,J77)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J77">
         <f>IF(B15&lt;=Расчет!D9+Расчет!D10,0,K77)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K77">
         <f>IF(B15&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,Расчет!D12+Расчет!D13,B15-(Расчет!D9+Расчет!D10))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L77" s="15">
         <f>IF(K77&lt;=0,0,K77)</f>
-        <v>5</v>
-      </c>
-      <c r="M77" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M77" s="331"/>
     </row>
     <row r="78" spans="1:17">
       <c r="H78" s="7"/>
       <c r="L78" s="7"/>
-      <c r="M78" s="333"/>
+      <c r="M78" s="331"/>
     </row>
     <row r="79" spans="1:17">
       <c r="H79" s="20">
@@ -20739,26 +20733,26 @@
       </c>
       <c r="I79">
         <f>IF(Расчет!D15+Расчет!D16&lt;=0,0,J79)</f>
-        <v>6.3999999999999986</v>
+        <v>1.5999999999999996</v>
       </c>
       <c r="J79">
         <f>IF(B15&lt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,0,K79)</f>
-        <v>6.3999999999999986</v>
+        <v>1.5999999999999996</v>
       </c>
       <c r="K79">
         <f>IF(B15&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,Расчет!D15+Расчет!D16,B15-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13))</f>
-        <v>6.3999999999999986</v>
+        <v>1.5999999999999996</v>
       </c>
       <c r="L79" s="15">
         <f>IF(K79&lt;=0,0,K79)</f>
-        <v>6.3999999999999986</v>
-      </c>
-      <c r="M79" s="333"/>
+        <v>1.5999999999999996</v>
+      </c>
+      <c r="M79" s="331"/>
     </row>
     <row r="80" spans="1:17">
       <c r="H80" s="7"/>
       <c r="L80" s="7"/>
-      <c r="M80" s="333"/>
+      <c r="M80" s="331"/>
     </row>
     <row r="81" spans="8:13" ht="13.5" thickBot="1">
       <c r="H81" s="20">
@@ -20774,13 +20768,13 @@
       </c>
       <c r="K81">
         <f>IF(B15&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16+Расчет!D18+Расчет!D19,Расчет!D18+Расчет!D19,B15-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16))</f>
-        <v>-2.6000000000000014</v>
+        <v>-0.40000000000000036</v>
       </c>
       <c r="L81" s="15">
         <f>IF(K81&lt;=0,0,K81)</f>
         <v>0</v>
       </c>
-      <c r="M81" s="333"/>
+      <c r="M81" s="331"/>
     </row>
     <row r="82" spans="8:13" ht="15" thickBot="1">
       <c r="H82" s="21" t="s">
@@ -20791,7 +20785,7 @@
       </c>
       <c r="J82" s="25">
         <f>SQRT((SUMSQ(L75*(Расчет!E9+Расчет!E10)+L77*(Расчет!E12+Расчет!E13)+L79*(Расчет!E15+Расчет!E16)+L81*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F5+L75*(Расчет!F9+Расчет!F10)+L77*(Расчет!F12+Расчет!F13)+L79*(Расчет!F15+Расчет!F16)+L81*(Расчет!F18+Расчет!F19))))</f>
-        <v>17.85329633304605</v>
+        <v>23.990608516667514</v>
       </c>
       <c r="K82" s="160" t="s">
         <v>141</v>
@@ -20825,7 +20819,7 @@
     <row r="85" spans="8:13" ht="12.75" customHeight="1">
       <c r="H85" s="7"/>
       <c r="L85" s="7"/>
-      <c r="M85" s="333" t="b">
+      <c r="M85" s="331" t="b">
         <f>IF(L86+L88+L90+L92=B16,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -20836,26 +20830,26 @@
       </c>
       <c r="I86">
         <f>IF(Расчет!D9+Расчет!D10&gt;=B16,B16,K86)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J86">
         <f>IF(Расчет!D9+Расчет!D10=B16,B16,K86)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K86">
         <f>IF(Расчет!D9+Расчет!D10&lt;B16,Расчет!D9+Расчет!D10,I86)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L86" s="15">
         <f>IF(K86&lt;=0,0,K86)</f>
-        <v>25</v>
-      </c>
-      <c r="M86" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M86" s="331"/>
     </row>
     <row r="87" spans="8:13">
       <c r="H87" s="7"/>
       <c r="L87" s="7"/>
-      <c r="M87" s="333"/>
+      <c r="M87" s="331"/>
     </row>
     <row r="88" spans="8:13">
       <c r="H88" s="20">
@@ -20863,26 +20857,26 @@
       </c>
       <c r="I88">
         <f>IF(Расчет!D12+Расчет!D13&lt;=0,0,J88)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J88">
         <f>IF(B16&lt;=Расчет!D9+Расчет!D10,0,K88)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K88">
         <f>IF(B16&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,Расчет!D12+Расчет!D13,B16-(Расчет!D9+Расчет!D10))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L88" s="15">
         <f>IF(K88&lt;=0,0,K88)</f>
-        <v>5</v>
-      </c>
-      <c r="M88" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M88" s="331"/>
     </row>
     <row r="89" spans="8:13">
       <c r="H89" s="7"/>
       <c r="L89" s="7"/>
-      <c r="M89" s="333"/>
+      <c r="M89" s="331"/>
     </row>
     <row r="90" spans="8:13">
       <c r="H90" s="20">
@@ -20890,26 +20884,26 @@
       </c>
       <c r="I90">
         <f>IF(Расчет!D15+Расчет!D16&lt;=0,0,J90)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J90">
         <f>IF(B16&lt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,0,K90)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K90">
         <f>IF(B16&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,Расчет!D15+Расчет!D16,B16-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13))</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L90" s="15">
         <f>IF(K90&lt;=0,0,K90)</f>
-        <v>9</v>
-      </c>
-      <c r="M90" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M90" s="331"/>
     </row>
     <row r="91" spans="8:13">
       <c r="H91" s="7"/>
       <c r="L91" s="7"/>
-      <c r="M91" s="333"/>
+      <c r="M91" s="331"/>
     </row>
     <row r="92" spans="8:13" ht="13.5" thickBot="1">
       <c r="H92" s="20">
@@ -20917,21 +20911,21 @@
       </c>
       <c r="I92">
         <f>IF(Расчет!D18+Расчет!D19&lt;=0,0,J92)</f>
-        <v>2.6000000000000014</v>
+        <v>0.40000000000000036</v>
       </c>
       <c r="J92">
         <f>IF(B16&lt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,0,K92)</f>
-        <v>2.6000000000000014</v>
+        <v>0.40000000000000036</v>
       </c>
       <c r="K92">
         <f>IF(B16&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16+Расчет!D18+Расчет!D19,Расчет!D18+Расчет!D19,B16-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16))</f>
-        <v>2.6000000000000014</v>
+        <v>0.40000000000000036</v>
       </c>
       <c r="L92" s="15">
         <f>IF(K92&lt;=0,0,K92)</f>
-        <v>2.6000000000000014</v>
-      </c>
-      <c r="M92" s="333"/>
+        <v>0.40000000000000036</v>
+      </c>
+      <c r="M92" s="331"/>
     </row>
     <row r="93" spans="8:13" ht="15" thickBot="1">
       <c r="H93" s="21" t="s">
@@ -20942,7 +20936,7 @@
       </c>
       <c r="J93" s="25">
         <f>SQRT((SUMSQ(L86*(Расчет!E9+Расчет!E10)+L88*(Расчет!E12+Расчет!E13)+L90*(Расчет!E15+Расчет!E16)+L92*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F5+L86*(Расчет!F9+Расчет!F10)+L88*(Расчет!F12+Расчет!F13)+L90*(Расчет!F15+Расчет!F16)+L92*(Расчет!F18+Расчет!F19))))</f>
-        <v>20.73484397551351</v>
+        <v>27.406211285035372</v>
       </c>
       <c r="K93" s="160" t="s">
         <v>141</v>
@@ -20976,7 +20970,7 @@
     <row r="96" spans="8:13" ht="12.75" customHeight="1">
       <c r="H96" s="7"/>
       <c r="L96" s="7"/>
-      <c r="M96" s="333" t="b">
+      <c r="M96" s="331" t="b">
         <f>IF(L97+L99+L101+L103=B17,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -20987,26 +20981,26 @@
       </c>
       <c r="I97">
         <f>IF(Расчет!D9+Расчет!D10&gt;=B17,B17,K97)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J97">
         <f>IF(Расчет!D9+Расчет!D10=B17,B17,K97)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K97">
         <f>IF(Расчет!D9+Расчет!D10&lt;B17,Расчет!D9+Расчет!D10,I97)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L97" s="15">
         <f>IF(K97&lt;=0,0,K97)</f>
-        <v>25</v>
-      </c>
-      <c r="M97" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M97" s="331"/>
     </row>
     <row r="98" spans="8:13">
       <c r="H98" s="7"/>
       <c r="L98" s="7"/>
-      <c r="M98" s="333"/>
+      <c r="M98" s="331"/>
     </row>
     <row r="99" spans="8:13">
       <c r="H99" s="20">
@@ -21014,26 +21008,26 @@
       </c>
       <c r="I99">
         <f>IF(Расчет!D12+Расчет!D13&lt;=0,0,J99)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J99">
         <f>IF(B17&lt;=Расчет!D9+Расчет!D10,0,K99)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K99">
         <f>IF(B17&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,Расчет!D12+Расчет!D13,B17-(Расчет!D9+Расчет!D10))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L99" s="15">
         <f>IF(K99&lt;=0,0,K99)</f>
-        <v>5</v>
-      </c>
-      <c r="M99" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M99" s="331"/>
     </row>
     <row r="100" spans="8:13">
       <c r="H100" s="7"/>
       <c r="L100" s="7"/>
-      <c r="M100" s="333"/>
+      <c r="M100" s="331"/>
     </row>
     <row r="101" spans="8:13">
       <c r="H101" s="20">
@@ -21041,26 +21035,26 @@
       </c>
       <c r="I101">
         <f>IF(Расчет!D15+Расчет!D16&lt;=0,0,J101)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J101">
         <f>IF(B17&lt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,0,K101)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K101">
         <f>IF(B17&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,Расчет!D15+Расчет!D16,B17-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13))</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L101" s="15">
         <f>IF(K101&lt;=0,0,K101)</f>
-        <v>9</v>
-      </c>
-      <c r="M101" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M101" s="331"/>
     </row>
     <row r="102" spans="8:13">
       <c r="H102" s="7"/>
       <c r="L102" s="7"/>
-      <c r="M102" s="333"/>
+      <c r="M102" s="331"/>
     </row>
     <row r="103" spans="8:13" ht="13.5" thickBot="1">
       <c r="H103" s="20">
@@ -21068,21 +21062,21 @@
       </c>
       <c r="I103">
         <f>IF(Расчет!D18+Расчет!D19&lt;=0,0,J103)</f>
-        <v>7.8000000000000043</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J103">
         <f>IF(B17&lt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,0,K103)</f>
-        <v>7.8000000000000043</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="K103">
         <f>IF(B17&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16+Расчет!D18+Расчет!D19,Расчет!D18+Расчет!D19,B17-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16))</f>
-        <v>7.8000000000000043</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="L103" s="15">
         <f>IF(K103&lt;=0,0,K103)</f>
-        <v>7.8000000000000043</v>
-      </c>
-      <c r="M103" s="333"/>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="M103" s="331"/>
     </row>
     <row r="104" spans="8:13" ht="15" thickBot="1">
       <c r="H104" s="21" t="s">
@@ -21093,7 +21087,7 @@
       </c>
       <c r="J104" s="25">
         <f>SQRT((SUMSQ(L97*(Расчет!E9+Расчет!E10)+L99*(Расчет!E12+Расчет!E13)+L101*(Расчет!E15+Расчет!E16)+L103*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F5+L97*(Расчет!F9+Расчет!F10)+L99*(Расчет!F12+Расчет!F13)+L101*(Расчет!F15+Расчет!F16)+L103*(Расчет!F18+Расчет!F19))))</f>
-        <v>24.283305104078764</v>
+        <v>30.822001768217458</v>
       </c>
       <c r="K104" s="160" t="s">
         <v>141</v>
@@ -21127,7 +21121,7 @@
     <row r="107" spans="8:13" ht="12.75" customHeight="1">
       <c r="H107" s="7"/>
       <c r="L107" s="7"/>
-      <c r="M107" s="333" t="b">
+      <c r="M107" s="331" t="b">
         <f>IF(L108+L110+L112+L114=B18,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -21138,26 +21132,26 @@
       </c>
       <c r="I108">
         <f>IF(Расчет!D9+Расчет!D10&gt;=B18,B18,K108)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J108">
         <f>IF(Расчет!D9+Расчет!D10=B18,B18,K108)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K108">
         <f>IF(Расчет!D9+Расчет!D10&lt;B18,Расчет!D9+Расчет!D10,I108)</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L108" s="15">
         <f>IF(K108&lt;=0,0,K108)</f>
-        <v>25</v>
-      </c>
-      <c r="M108" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M108" s="331"/>
     </row>
     <row r="109" spans="8:13">
       <c r="H109" s="7"/>
       <c r="L109" s="7"/>
-      <c r="M109" s="333"/>
+      <c r="M109" s="331"/>
     </row>
     <row r="110" spans="8:13">
       <c r="H110" s="20">
@@ -21165,26 +21159,26 @@
       </c>
       <c r="I110">
         <f>IF(Расчет!D12+Расчет!D13&lt;=0,0,J110)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J110">
         <f>IF(B18&lt;=Расчет!D9+Расчет!D10,0,K110)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K110">
         <f>IF(B18&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,Расчет!D12+Расчет!D13,B18-(Расчет!D9+Расчет!D10))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L110" s="15">
         <f>IF(K110&lt;=0,0,K110)</f>
-        <v>5</v>
-      </c>
-      <c r="M110" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M110" s="331"/>
     </row>
     <row r="111" spans="8:13">
       <c r="H111" s="7"/>
       <c r="L111" s="7"/>
-      <c r="M111" s="333"/>
+      <c r="M111" s="331"/>
     </row>
     <row r="112" spans="8:13">
       <c r="H112" s="20">
@@ -21192,26 +21186,26 @@
       </c>
       <c r="I112">
         <f>IF(Расчет!D15+Расчет!D16&lt;=0,0,J112)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J112">
         <f>IF(B18&lt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13,0,K112)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K112">
         <f>IF(B18&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,Расчет!D15+Расчет!D16,B18-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13))</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L112" s="15">
         <f>IF(K112&lt;=0,0,K112)</f>
-        <v>9</v>
-      </c>
-      <c r="M112" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M112" s="331"/>
     </row>
     <row r="113" spans="2:13">
       <c r="H113" s="7"/>
       <c r="L113" s="7"/>
-      <c r="M113" s="333"/>
+      <c r="M113" s="331"/>
     </row>
     <row r="114" spans="2:13" ht="13.5" thickBot="1">
       <c r="H114" s="20">
@@ -21219,21 +21213,21 @@
       </c>
       <c r="I114">
         <f>IF(Расчет!D18+Расчет!D19&lt;=0,0,J114)</f>
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J114">
         <f>IF(B18&lt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16,0,K114)</f>
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K114">
         <f>IF(B18&gt;=Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16+Расчет!D18+Расчет!D19,Расчет!D18+Расчет!D19,B18-(Расчет!D9+Расчет!D10+Расчет!D12+Расчет!D13+Расчет!D15+Расчет!D16))</f>
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L114" s="15">
         <f>IF(K114&lt;=0,0,K114)</f>
-        <v>13</v>
-      </c>
-      <c r="M114" s="333"/>
+        <v>2</v>
+      </c>
+      <c r="M114" s="331"/>
     </row>
     <row r="115" spans="2:13" ht="12.75" customHeight="1" thickBot="1">
       <c r="H115" s="21" t="s">
@@ -21244,7 +21238,7 @@
       </c>
       <c r="J115" s="25">
         <f>SQRT((SUMSQ(L108*(Расчет!E9+Расчет!E10)+L110*(Расчет!E12+Расчет!E13)+L112*(Расчет!E15+Расчет!E16)+L114*(Расчет!E18+Расчет!E19)))+(SUMSQ(Расчет!F5+L108*(Расчет!F9+Расчет!F10)+L110*(Расчет!F12+Расчет!F13)+L112*(Расчет!F15+Расчет!F16)+L114*(Расчет!F18+Расчет!F19))))</f>
-        <v>28.0424841762954</v>
+        <v>34.23792378343056</v>
       </c>
       <c r="K115" s="160" t="s">
         <v>141</v>
@@ -21270,7 +21264,7 @@
       </c>
       <c r="J118" s="194">
         <f>IFERROR(SQRT((SUMSQ((Расчет!D28+Расчет!D29)*(Расчет!E28+Расчет!E29)+(Расчет!D31+Расчет!D32)*(Расчет!E31+Расчет!E32)+(Расчет!D34+Расчет!D35)*(Расчет!E34+Расчет!E35)+(Расчет!D37+Расчет!D38)*(Расчет!E37+Расчет!E38)))+(SUMSQ(Расчет!E5+Расчет!E26+(Расчет!D28+Расчет!D29)*(Расчет!F28+Расчет!F29)+(Расчет!D31+Расчет!D32)*(Расчет!F31+Расчет!F32)+(Расчет!D34+Расчет!D35)*(Расчет!F34+Расчет!F35)+(Расчет!D37+Расчет!D38)*(Расчет!F37+Расчет!F38)))),"---")</f>
-        <v>15.816402599165491</v>
+        <v>36.885315506309553</v>
       </c>
       <c r="K118" s="177" t="s">
         <v>141</v>
@@ -21585,50 +21579,50 @@
       </c>
       <c r="C145">
         <f>(B145-B146)/10</f>
-        <v>443.32243615150657</v>
+        <v>458.63050959819492</v>
       </c>
       <c r="D145" s="75">
         <v>0</v>
       </c>
       <c r="E145">
         <f>B145-C145</f>
-        <v>5034.9384334137112</v>
+        <v>5019.6303599670227</v>
       </c>
       <c r="F145">
         <f>B145-2*C145</f>
-        <v>4591.6159972622045</v>
+        <v>4560.9998503688284</v>
       </c>
       <c r="G145">
         <f>B145-3*C145</f>
-        <v>4148.2935611106986</v>
+        <v>4102.3693407706332</v>
       </c>
       <c r="H145">
         <f>B145-4*C145</f>
-        <v>3704.9711249591919</v>
+        <v>3643.738831172438</v>
       </c>
       <c r="I145">
         <f>B145-5*C145</f>
-        <v>3261.6486888076852</v>
+        <v>3185.1083215742433</v>
       </c>
       <c r="J145">
         <f>B145-6*C145</f>
-        <v>2818.3262526561784</v>
+        <v>2726.4778119760485</v>
       </c>
       <c r="K145">
         <f>B145-7*C145</f>
-        <v>2375.0038165046722</v>
+        <v>2267.8473023778533</v>
       </c>
       <c r="L145">
         <f>B145-8*C145</f>
-        <v>1931.6813803531654</v>
+        <v>1809.2167927796586</v>
       </c>
       <c r="M145">
         <f>B145-9*C145</f>
-        <v>1488.3589442016587</v>
+        <v>1350.5862831814638</v>
       </c>
       <c r="N145" s="8">
         <f>B145-10*C145</f>
-        <v>1045.0365080501524</v>
+        <v>891.95577358326864</v>
       </c>
       <c r="Q145" s="78" t="e">
         <f>P20</f>
@@ -21685,54 +21679,54 @@
     <row r="146" spans="2:29">
       <c r="B146" s="78">
         <f t="shared" si="2"/>
-        <v>1045.0365080501524</v>
+        <v>891.95577358326875</v>
       </c>
       <c r="C146">
         <f t="shared" ref="C146:C154" si="14">(B146-B147)/10</f>
-        <v>47.229005555856951</v>
+        <v>43.709119505265363</v>
       </c>
       <c r="D146" s="75">
         <v>10</v>
       </c>
       <c r="E146">
         <f t="shared" ref="E146:E154" si="15">B146-C146</f>
-        <v>997.80750249429548</v>
+        <v>848.24665407800342</v>
       </c>
       <c r="F146">
         <f t="shared" ref="F146:F154" si="16">B146-2*C146</f>
-        <v>950.57849693843855</v>
+        <v>804.53753457273797</v>
       </c>
       <c r="G146">
         <f t="shared" ref="G146:G154" si="17">B146-3*C146</f>
-        <v>903.34949138258162</v>
+        <v>760.82841506747263</v>
       </c>
       <c r="H146">
         <f t="shared" ref="H146:H154" si="18">B146-4*C146</f>
-        <v>856.12048582672458</v>
+        <v>717.1192955622073</v>
       </c>
       <c r="I146">
         <f t="shared" ref="I146:I154" si="19">B146-5*C146</f>
-        <v>808.89148027086765</v>
+        <v>673.41017605694196</v>
       </c>
       <c r="J146">
         <f t="shared" ref="J146:J154" si="20">B146-6*C146</f>
-        <v>761.66247471501072</v>
+        <v>629.70105655167663</v>
       </c>
       <c r="K146">
         <f t="shared" ref="K146:K154" si="21">B146-7*C146</f>
-        <v>714.43346915915367</v>
+        <v>585.99193704641118</v>
       </c>
       <c r="L146">
         <f t="shared" ref="L146:L154" si="22">B146-8*C146</f>
-        <v>667.20446360329674</v>
+        <v>542.28281754114585</v>
       </c>
       <c r="M146">
         <f t="shared" ref="M146:M154" si="23">B146-9*C146</f>
-        <v>619.97545804743982</v>
+        <v>498.57369803588051</v>
       </c>
       <c r="N146" s="8">
         <f t="shared" ref="N146:N154" si="24">B146-10*C146</f>
-        <v>572.74645249158289</v>
+        <v>454.86457853061512</v>
       </c>
       <c r="Q146" s="78" t="e">
         <f t="shared" ref="Q146:Q155" si="25">P21</f>
@@ -21789,54 +21783,54 @@
     <row r="147" spans="2:29">
       <c r="B147" s="78">
         <f t="shared" si="2"/>
-        <v>572.74645249158289</v>
+        <v>454.86457853061512</v>
       </c>
       <c r="C147">
         <f t="shared" si="14"/>
-        <v>17.843372514787621</v>
+        <v>15.003957028664871</v>
       </c>
       <c r="D147" s="75">
         <v>20</v>
       </c>
       <c r="E147">
         <f t="shared" si="15"/>
-        <v>554.90307997679531</v>
+        <v>439.86062150195028</v>
       </c>
       <c r="F147">
         <f t="shared" si="16"/>
-        <v>537.05970746200762</v>
+        <v>424.85666447328538</v>
       </c>
       <c r="G147">
         <f t="shared" si="17"/>
-        <v>519.21633494722005</v>
+        <v>409.85270744462048</v>
       </c>
       <c r="H147">
         <f t="shared" si="18"/>
-        <v>501.37296243243242</v>
+        <v>394.84875041595564</v>
       </c>
       <c r="I147">
         <f t="shared" si="19"/>
-        <v>483.52958991764478</v>
+        <v>379.84479338729079</v>
       </c>
       <c r="J147">
         <f t="shared" si="20"/>
-        <v>465.68621740285715</v>
+        <v>364.84083635862589</v>
       </c>
       <c r="K147">
         <f t="shared" si="21"/>
-        <v>447.84284488806952</v>
+        <v>349.83687932996099</v>
       </c>
       <c r="L147">
         <f t="shared" si="22"/>
-        <v>429.99947237328195</v>
+        <v>334.83292230129615</v>
       </c>
       <c r="M147">
         <f t="shared" si="23"/>
-        <v>412.15609985849426</v>
+        <v>319.82896527263131</v>
       </c>
       <c r="N147" s="8">
         <f t="shared" si="24"/>
-        <v>394.31272734370668</v>
+        <v>304.82500824396641</v>
       </c>
       <c r="Q147" s="78" t="e">
         <f t="shared" si="25"/>
@@ -21893,54 +21887,54 @@
     <row r="148" spans="2:29">
       <c r="B148" s="78">
         <f t="shared" si="2"/>
-        <v>394.31272734370668</v>
+        <v>304.82500824396641</v>
       </c>
       <c r="C148">
         <f t="shared" si="14"/>
-        <v>9.3690599545900959</v>
+        <v>7.5672866367780163</v>
       </c>
       <c r="D148" s="75">
         <v>30</v>
       </c>
       <c r="E148">
         <f t="shared" si="15"/>
-        <v>384.94366738911657</v>
+        <v>297.25772160718839</v>
       </c>
       <c r="F148">
         <f t="shared" si="16"/>
-        <v>375.57460743452651</v>
+        <v>289.69043497041037</v>
       </c>
       <c r="G148">
         <f t="shared" si="17"/>
-        <v>366.2055474799364</v>
+        <v>282.12314833363234</v>
       </c>
       <c r="H148">
         <f t="shared" si="18"/>
-        <v>356.83648752534629</v>
+        <v>274.55586169685432</v>
       </c>
       <c r="I148">
         <f t="shared" si="19"/>
-        <v>347.46742757075617</v>
+        <v>266.9885750600763</v>
       </c>
       <c r="J148">
         <f t="shared" si="20"/>
-        <v>338.09836761616612</v>
+        <v>259.42128842329828</v>
       </c>
       <c r="K148">
         <f t="shared" si="21"/>
-        <v>328.729307661576</v>
+        <v>251.85400178652029</v>
       </c>
       <c r="L148">
         <f t="shared" si="22"/>
-        <v>319.36024770698589</v>
+        <v>244.28671514974229</v>
       </c>
       <c r="M148">
         <f t="shared" si="23"/>
-        <v>309.99118775239583</v>
+        <v>236.71942851296427</v>
       </c>
       <c r="N148" s="8">
         <f t="shared" si="24"/>
-        <v>300.62212779780572</v>
+        <v>229.15214187618625</v>
       </c>
       <c r="Q148" s="78" t="e">
         <f t="shared" si="25"/>
@@ -21997,54 +21991,54 @@
     <row r="149" spans="2:29">
       <c r="B149" s="78">
         <f t="shared" si="2"/>
-        <v>300.62212779780572</v>
+        <v>229.15214187618625</v>
       </c>
       <c r="C149">
         <f t="shared" si="14"/>
-        <v>5.7565692728318112</v>
+        <v>4.5590141998974847</v>
       </c>
       <c r="D149" s="75">
         <v>40</v>
       </c>
       <c r="E149">
         <f t="shared" si="15"/>
-        <v>294.86555852497389</v>
+        <v>224.59312767628876</v>
       </c>
       <c r="F149">
         <f t="shared" si="16"/>
-        <v>289.10898925214212</v>
+        <v>220.03411347639127</v>
       </c>
       <c r="G149">
         <f t="shared" si="17"/>
-        <v>283.3524199793103</v>
+        <v>215.47509927649381</v>
       </c>
       <c r="H149">
         <f t="shared" si="18"/>
-        <v>277.59585070647847</v>
+        <v>210.91608507659632</v>
       </c>
       <c r="I149">
         <f t="shared" si="19"/>
-        <v>271.83928143364665</v>
+        <v>206.35707087669883</v>
       </c>
       <c r="J149">
         <f t="shared" si="20"/>
-        <v>266.08271216081482</v>
+        <v>201.79805667680134</v>
       </c>
       <c r="K149">
         <f t="shared" si="21"/>
-        <v>260.32614288798305</v>
+        <v>197.23904247690385</v>
       </c>
       <c r="L149">
         <f t="shared" si="22"/>
-        <v>254.56957361515123</v>
+        <v>192.68002827700639</v>
       </c>
       <c r="M149">
         <f t="shared" si="23"/>
-        <v>248.8130043423194</v>
+        <v>188.1210140771089</v>
       </c>
       <c r="N149" s="8">
         <f t="shared" si="24"/>
-        <v>243.05643506948761</v>
+        <v>183.56199987721141</v>
       </c>
       <c r="Q149" s="78" t="e">
         <f t="shared" si="25"/>
@@ -22101,54 +22095,54 @@
     <row r="150" spans="2:29">
       <c r="B150" s="78">
         <f t="shared" si="2"/>
-        <v>243.05643506948761</v>
+        <v>183.56199987721141</v>
       </c>
       <c r="C150">
         <f t="shared" si="14"/>
-        <v>3.8598207275276053</v>
+        <v>3.0465714613572117</v>
       </c>
       <c r="D150" s="75">
         <v>50</v>
       </c>
       <c r="E150">
         <f t="shared" si="15"/>
-        <v>239.19661434196001</v>
+        <v>180.51542841585419</v>
       </c>
       <c r="F150">
         <f t="shared" si="16"/>
-        <v>235.33679361443239</v>
+        <v>177.46885695449697</v>
       </c>
       <c r="G150">
         <f t="shared" si="17"/>
-        <v>231.47697288690478</v>
+        <v>174.42228549313978</v>
       </c>
       <c r="H150">
         <f t="shared" si="18"/>
-        <v>227.61715215937718</v>
+        <v>171.37571403178256</v>
       </c>
       <c r="I150">
         <f t="shared" si="19"/>
-        <v>223.75733143184959</v>
+        <v>168.32914257042535</v>
       </c>
       <c r="J150">
         <f t="shared" si="20"/>
-        <v>219.89751070432197</v>
+        <v>165.28257110906813</v>
       </c>
       <c r="K150">
         <f t="shared" si="21"/>
-        <v>216.03768997679435</v>
+        <v>162.23599964771091</v>
       </c>
       <c r="L150">
         <f t="shared" si="22"/>
-        <v>212.17786924926676</v>
+        <v>159.18942818635372</v>
       </c>
       <c r="M150">
         <f t="shared" si="23"/>
-        <v>208.31804852173917</v>
+        <v>156.14285672499651</v>
       </c>
       <c r="N150" s="8">
         <f t="shared" si="24"/>
-        <v>204.45822779421155</v>
+        <v>153.09628526363929</v>
       </c>
       <c r="Q150" s="78" t="e">
         <f t="shared" si="25"/>
@@ -22205,54 +22199,54 @@
     <row r="151" spans="2:29">
       <c r="B151" s="78">
         <f t="shared" si="2"/>
-        <v>204.45822779421155</v>
+        <v>153.09628526363929</v>
       </c>
       <c r="C151">
         <f t="shared" si="14"/>
-        <v>2.8020222103944663</v>
+        <v>2.1794905483650266</v>
       </c>
       <c r="D151" s="75">
         <v>60</v>
       </c>
       <c r="E151">
         <f t="shared" si="15"/>
-        <v>201.6562055838171</v>
+        <v>150.91679471527425</v>
       </c>
       <c r="F151">
         <f t="shared" si="16"/>
-        <v>198.85418337342261</v>
+        <v>148.73730416690924</v>
       </c>
       <c r="G151">
         <f t="shared" si="17"/>
-        <v>196.05216116302816</v>
+        <v>146.5578136185442</v>
       </c>
       <c r="H151">
         <f t="shared" si="18"/>
-        <v>193.25013895263368</v>
+        <v>144.37832307017919</v>
       </c>
       <c r="I151">
         <f t="shared" si="19"/>
-        <v>190.44811674223922</v>
+        <v>142.19883252181415</v>
       </c>
       <c r="J151">
         <f t="shared" si="20"/>
-        <v>187.64609453184477</v>
+        <v>140.01934197344912</v>
       </c>
       <c r="K151">
         <f t="shared" si="21"/>
-        <v>184.84407232145028</v>
+        <v>137.83985142508411</v>
       </c>
       <c r="L151">
         <f t="shared" si="22"/>
-        <v>182.04205011105583</v>
+        <v>135.66036087671907</v>
       </c>
       <c r="M151">
         <f t="shared" si="23"/>
-        <v>179.24002790066135</v>
+        <v>133.48087032835406</v>
       </c>
       <c r="N151" s="8">
         <f t="shared" si="24"/>
-        <v>176.43800569026689</v>
+        <v>131.30137977998902</v>
       </c>
       <c r="Q151" s="78" t="e">
         <f t="shared" si="25"/>
@@ -22309,54 +22303,54 @@
     <row r="152" spans="2:29">
       <c r="B152" s="78">
         <f t="shared" si="2"/>
-        <v>176.43800569026689</v>
+        <v>131.30137977998902</v>
       </c>
       <c r="C152">
         <f t="shared" si="14"/>
-        <v>2.4519814083908842</v>
+        <v>1.636393121262735</v>
       </c>
       <c r="D152" s="75">
         <v>70</v>
       </c>
       <c r="E152">
         <f t="shared" si="15"/>
-        <v>173.98602428187601</v>
+        <v>129.66498665872629</v>
       </c>
       <c r="F152">
         <f t="shared" si="16"/>
-        <v>171.53404287348513</v>
+        <v>128.02859353746356</v>
       </c>
       <c r="G152">
         <f t="shared" si="17"/>
-        <v>169.08206146509423</v>
+        <v>126.39220041620081</v>
       </c>
       <c r="H152">
         <f t="shared" si="18"/>
-        <v>166.63008005670335</v>
+        <v>124.75580729493808</v>
       </c>
       <c r="I152">
         <f t="shared" si="19"/>
-        <v>164.17809864831247</v>
+        <v>123.11941417367535</v>
       </c>
       <c r="J152">
         <f t="shared" si="20"/>
-        <v>161.72611723992159</v>
+        <v>121.48302105241261</v>
       </c>
       <c r="K152">
         <f t="shared" si="21"/>
-        <v>159.27413583153071</v>
+        <v>119.84662793114987</v>
       </c>
       <c r="L152">
         <f t="shared" si="22"/>
-        <v>156.82215442313981</v>
+        <v>118.21023480988714</v>
       </c>
       <c r="M152">
         <f t="shared" si="23"/>
-        <v>154.37017301474893</v>
+        <v>116.57384168862441</v>
       </c>
       <c r="N152" s="8">
         <f t="shared" si="24"/>
-        <v>151.91819160635805</v>
+        <v>114.93744856736167</v>
       </c>
       <c r="Q152" s="78" t="e">
         <f t="shared" si="25"/>
@@ -22413,54 +22407,54 @@
     <row r="153" spans="2:29">
       <c r="B153" s="78">
         <f t="shared" si="2"/>
-        <v>151.91819160635805</v>
+        <v>114.93744856736167</v>
       </c>
       <c r="C153">
         <f t="shared" si="14"/>
-        <v>2.2199440946222095</v>
+        <v>1.2737726963031377</v>
       </c>
       <c r="D153" s="75">
         <v>80</v>
       </c>
       <c r="E153">
         <f t="shared" si="15"/>
-        <v>149.69824751173584</v>
+        <v>113.66367587105853</v>
       </c>
       <c r="F153">
         <f t="shared" si="16"/>
-        <v>147.47830341711364</v>
+        <v>112.38990317475539</v>
       </c>
       <c r="G153">
         <f t="shared" si="17"/>
-        <v>145.25835932249143</v>
+        <v>111.11613047845226</v>
       </c>
       <c r="H153">
         <f t="shared" si="18"/>
-        <v>143.03841522786922</v>
+        <v>109.84235778214912</v>
       </c>
       <c r="I153">
         <f t="shared" si="19"/>
-        <v>140.81847113324699</v>
+        <v>108.56858508584598</v>
       </c>
       <c r="J153">
         <f t="shared" si="20"/>
-        <v>138.59852703862478</v>
+        <v>107.29481238954284</v>
       </c>
       <c r="K153">
         <f t="shared" si="21"/>
-        <v>136.37858294400257</v>
+        <v>106.0210396932397</v>
       </c>
       <c r="L153">
         <f t="shared" si="22"/>
-        <v>134.15863884938037</v>
+        <v>104.74726699693657</v>
       </c>
       <c r="M153">
         <f t="shared" si="23"/>
-        <v>131.93869475475816</v>
+        <v>103.47349430063343</v>
       </c>
       <c r="N153" s="8">
         <f t="shared" si="24"/>
-        <v>129.71875066013595</v>
+        <v>102.19972160433029</v>
       </c>
       <c r="Q153" s="78" t="e">
         <f t="shared" si="25"/>
@@ -22517,54 +22511,54 @@
     <row r="154" spans="2:29">
       <c r="B154" s="78">
         <f t="shared" si="2"/>
-        <v>129.71875066013595</v>
+        <v>102.19972160433029</v>
       </c>
       <c r="C154">
         <f t="shared" si="14"/>
-        <v>1.7389187409005458</v>
+        <v>1.0196479237033416</v>
       </c>
       <c r="D154" s="75">
         <v>90</v>
       </c>
       <c r="E154">
         <f t="shared" si="15"/>
-        <v>127.97983191923541</v>
+        <v>101.18007368062695</v>
       </c>
       <c r="F154">
         <f t="shared" si="16"/>
-        <v>126.24091317833486</v>
+        <v>100.16042575692362</v>
       </c>
       <c r="G154">
         <f t="shared" si="17"/>
-        <v>124.50199443743432</v>
+        <v>99.14077783322027</v>
       </c>
       <c r="H154">
         <f t="shared" si="18"/>
-        <v>122.76307569653378</v>
+        <v>98.121129909516924</v>
       </c>
       <c r="I154">
         <f t="shared" si="19"/>
-        <v>121.02415695563323</v>
+        <v>97.101481985813592</v>
       </c>
       <c r="J154">
         <f t="shared" si="20"/>
-        <v>119.28523821473269</v>
+        <v>96.081834062110246</v>
       </c>
       <c r="K154">
         <f t="shared" si="21"/>
-        <v>117.54631947383213</v>
+        <v>95.062186138406901</v>
       </c>
       <c r="L154">
         <f t="shared" si="22"/>
-        <v>115.80740073293158</v>
+        <v>94.042538214703555</v>
       </c>
       <c r="M154">
         <f t="shared" si="23"/>
-        <v>114.06848199203104</v>
+        <v>93.022890291000223</v>
       </c>
       <c r="N154" s="8">
         <f t="shared" si="24"/>
-        <v>112.32956325113049</v>
+        <v>92.003242367296878</v>
       </c>
       <c r="Q154" s="78" t="e">
         <f t="shared" si="25"/>
@@ -22621,7 +22615,7 @@
     <row r="155" spans="2:29">
       <c r="B155" s="78">
         <f t="shared" si="2"/>
-        <v>112.32956325113049</v>
+        <v>92.003242367296878</v>
       </c>
       <c r="N155" s="8"/>
       <c r="Q155" s="78" t="e">
@@ -22698,7 +22692,7 @@
       <c r="B157" s="7"/>
       <c r="C157" s="80">
         <f>Расчет!K26</f>
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="E157" s="71">
         <v>10</v>
@@ -22772,7 +22766,7 @@
       </c>
       <c r="C158" s="86">
         <f>COUNTIF(E167:N177,"&gt;0")</f>
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D158" s="86" t="s">
         <v>104</v>
@@ -23400,39 +23394,39 @@
       </c>
       <c r="F168" s="73">
         <f>IF(C157&gt;F146,0,F157)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G168" s="73">
         <f>IF(C157&gt;G146,0,G157)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H168" s="73">
         <f>IF(C157&gt;H146,0,H157)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I168" s="73">
         <f>IF(C157&gt;I146,0,I157)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J168" s="73">
         <f>IF(C157&gt;J146,0,J157)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K168" s="73">
         <f>IF(C157&gt;K146,0,K157)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L168" s="73">
         <f>IF(C157&gt;L146,0,L157)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M168" s="73">
         <f>IF(C157&gt;M146,0,M157)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N168" s="81">
         <f>IF(C157&gt;N146,0,N157)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q168" s="7"/>
       <c r="T168" s="73" t="str">
@@ -23480,43 +23474,43 @@
       <c r="B169" s="7"/>
       <c r="E169" s="73">
         <f>IF(C157&gt;E147,0,E158)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F169" s="73">
         <f>IF(C157&gt;F147,0,F158)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G169" s="73">
         <f>IF(C157&gt;G147,0,G158)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H169" s="73">
         <f>IF(C157&gt;H147,0,H158)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I169" s="73">
         <f>IF(C157&gt;I147,0,I158)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J169" s="73">
         <f>IF(C157&gt;J147,0,J158)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K169" s="73">
         <f>IF(C157&gt;K147,0,K158)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L169" s="73">
         <f>IF(C157&gt;L147,0,L158)</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M169" s="73">
         <f>IF(C157&gt;M147,0,M158)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N169" s="81">
         <f>IF(C157&gt;N147,0,N158)</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q169" s="7"/>
       <c r="T169" s="73" t="str">
@@ -23564,43 +23558,43 @@
       <c r="B170" s="7"/>
       <c r="E170" s="73">
         <f>IF(C157&gt;E148,0,E159)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F170" s="73">
         <f>IF(C157&gt;F148,0,F159)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G170" s="73">
         <f>IF(C157&gt;G148,0,G159)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H170" s="73">
         <f>IF(C157&gt;H148,0,H159)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I170" s="73">
         <f>IF(C157&gt;I148,0,I159)</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J170" s="73">
         <f>IF(C157&gt;J148,0,J159)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K170" s="73">
         <f>IF(C157&gt;K148,0,K159)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L170" s="73">
         <f>IF(C157&gt;L148,0,L159)</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M170" s="73">
         <f>IF(C157&gt;M148,0,M159)</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N170" s="81">
         <f>IF(C157&gt;N148,0,N159)</f>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Q170" s="7"/>
       <c r="T170" s="73" t="str">
@@ -23648,43 +23642,43 @@
       <c r="B171" s="7"/>
       <c r="E171" s="73">
         <f>IF(C157&gt;E149,0,E160)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F171" s="73">
         <f>IF(C157&gt;F149,0,F160)</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G171" s="73">
         <f>IF(C157&gt;G149,0,G160)</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H171" s="73">
         <f>IF(C157&gt;H149,0,H160)</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I171" s="73">
         <f>IF(C157&gt;I149,0,I160)</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J171" s="73">
         <f>IF(C157&gt;J149,0,J160)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K171" s="73">
         <f>IF(C157&gt;K149,0,K160)</f>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L171" s="73">
         <f>IF(C157&gt;L149,0,L160)</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M171" s="73">
         <f>IF(C157&gt;M149,0,M160)</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="N171" s="81">
         <f>IF(C157&gt;N149,0,N160)</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q171" s="7"/>
       <c r="T171" s="73" t="str">
@@ -23732,43 +23726,43 @@
       <c r="B172" s="7"/>
       <c r="E172" s="73">
         <f>IF(C157&gt;E150,0,E161)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F172" s="73">
         <f>IF(C157&gt;F150,0,F161)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G172" s="73">
         <f>IF(C157&gt;G150,0,G161)</f>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H172" s="73">
         <f>IF(C157&gt;H150,0,H161)</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I172" s="73">
         <f>IF(C157&gt;I150,0,I161)</f>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J172" s="73">
         <f>IF(C157&gt;J150,0,J161)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K172" s="73">
         <f>IF(C157&gt;K150,0,K161)</f>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L172" s="73">
         <f>IF(C157&gt;L150,0,L161)</f>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M172" s="73">
         <f>IF(C157&gt;M150,0,M161)</f>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N172" s="81">
         <f>IF(C157&gt;N150,0,N161)</f>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="Q172" s="7"/>
       <c r="T172" s="73" t="str">
@@ -23816,43 +23810,43 @@
       <c r="B173" s="7"/>
       <c r="E173" s="73">
         <f>IF(C157&gt;E151,0,E162)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F173" s="73">
         <f>IF(C157&gt;F151,0,F162)</f>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G173" s="73">
         <f>IF(C157&gt;G151,0,G162)</f>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H173" s="73">
         <f>IF(C157&gt;H151,0,H162)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I173" s="73">
         <f>IF(C157&gt;I151,0,I162)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J173" s="73">
         <f>IF(C157&gt;J151,0,J162)</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="K173" s="73">
         <f>IF(C157&gt;K151,0,K162)</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L173" s="73">
         <f>IF(C157&gt;L151,0,L162)</f>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M173" s="73">
         <f>IF(C157&gt;M151,0,M162)</f>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="N173" s="81">
         <f>IF(C157&gt;N151,0,N162)</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Q173" s="7"/>
       <c r="T173" s="73" t="str">
@@ -23900,43 +23894,43 @@
       <c r="B174" s="7"/>
       <c r="E174" s="73">
         <f>IF(C157&gt;E152,0,E163)</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F174" s="73">
         <f>IF(C157&gt;F152,0,F163)</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="G174" s="73">
         <f>IF(C157&gt;G152,0,G163)</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H174" s="73">
         <f>IF(C157&gt;H152,0,H163)</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I174" s="73">
         <f>IF(C157&gt;I152,0,I163)</f>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J174" s="73">
         <f>IF(C157&gt;J152,0,J163)</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K174" s="73">
         <f>IF(C157&gt;K152,0,K163)</f>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L174" s="73">
         <f>IF(C157&gt;L152,0,L163)</f>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M174" s="73">
         <f>IF(C157&gt;M152,0,M163)</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N174" s="81">
         <f>IF(C157&gt;N152,0,N163)</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="Q174" s="7"/>
       <c r="T174" s="73" t="str">
@@ -23984,43 +23978,43 @@
       <c r="B175" s="7"/>
       <c r="E175" s="73">
         <f>IF(C157&gt;E153,0,E164)</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F175" s="73">
         <f>IF(C157&gt;F153,0,F164)</f>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G175" s="73">
         <f>IF(C157&gt;G153,0,G164)</f>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H175" s="73">
         <f>IF(C157&gt;H153,0,H164)</f>
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I175" s="73">
         <f>IF(C157&gt;I153,0,I164)</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="J175" s="73">
         <f>IF(C157&gt;J153,0,J164)</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K175" s="73">
         <f>IF(C157&gt;K153,0,K164)</f>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="L175" s="73">
         <f>IF(C157&gt;L153,0,L164)</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M175" s="73">
         <f>IF(C157&gt;M153,0,M164)</f>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N175" s="81">
         <f>IF(C157&gt;N153,0,N164)</f>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="Q175" s="7"/>
       <c r="T175" s="73" t="str">
@@ -24068,43 +24062,43 @@
       <c r="B176" s="7"/>
       <c r="E176" s="73">
         <f>IF(C157&gt;E154,0,E165)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F176" s="73">
         <f>IF(C157&gt;F154,0,F165)</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G176" s="73">
         <f>IF(C157&gt;G154,0,G165)</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H176" s="73">
         <f>IF(C157&gt;H154,0,H165)</f>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="I176" s="73">
         <f>IF(C157&gt;I154,0,I165)</f>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J176" s="73">
         <f>IF(C157&gt;J154,0,J165)</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K176" s="73">
         <f>IF(C157&gt;K154,0,K165)</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L176" s="73">
         <f>IF(C157&gt;L154,0,L165)</f>
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M176" s="73">
         <f>IF(C157&gt;M154,0,M165)</f>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="N176" s="81">
         <f>IF(C157&gt;N154,0,N165)</f>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="Q176" s="7"/>
       <c r="T176" s="73" t="str">
@@ -24152,7 +24146,7 @@
       <c r="B177" s="7"/>
       <c r="E177" s="73">
         <f>IF(C157&gt;E154,0,E166)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N177" s="8"/>
       <c r="Q177" s="7"/>
@@ -24241,50 +24235,50 @@
       </c>
       <c r="C180">
         <f>(B180-B181)/10</f>
-        <v>295.54829076767101</v>
+        <v>305.75367306546326</v>
       </c>
       <c r="D180" s="75">
         <v>0</v>
       </c>
       <c r="E180">
         <f>B180-C180</f>
-        <v>3356.6256222758075</v>
+        <v>3346.4202399780152</v>
       </c>
       <c r="F180">
         <f>B180-2*C180</f>
-        <v>3061.0773315081365</v>
+        <v>3040.6665669125518</v>
       </c>
       <c r="G180">
         <f>B180-3*C180</f>
-        <v>2765.5290407404655</v>
+        <v>2734.9128938470885</v>
       </c>
       <c r="H180">
         <f>B180-4*C180</f>
-        <v>2469.9807499727945</v>
+        <v>2429.1592207816257</v>
       </c>
       <c r="I180">
         <f>B180-5*C180</f>
-        <v>2174.4324592051235</v>
+        <v>2123.4055477161619</v>
       </c>
       <c r="J180">
         <f>B180-6*C180</f>
-        <v>1878.8841684374524</v>
+        <v>1817.651874650699</v>
       </c>
       <c r="K180">
         <f>B180-7*C180</f>
-        <v>1583.3358776697814</v>
+        <v>1511.8982015852357</v>
       </c>
       <c r="L180">
         <f>B180-8*C180</f>
-        <v>1287.7875869021104</v>
+        <v>1206.1445285197724</v>
       </c>
       <c r="M180">
         <f>B180-9*C180</f>
-        <v>992.23929613443943</v>
+        <v>900.39085545430908</v>
       </c>
       <c r="N180" s="8">
         <f>B180-10*C180</f>
-        <v>696.69100536676842</v>
+        <v>594.63718238884576</v>
       </c>
       <c r="Q180" s="78" t="e">
         <f>R20</f>
@@ -24341,54 +24335,54 @@
     <row r="181" spans="2:29">
       <c r="B181" s="78">
         <f t="shared" si="29"/>
-        <v>696.69100536676831</v>
+        <v>594.63718238884587</v>
       </c>
       <c r="C181">
         <f t="shared" ref="C181:C189" si="41">(B181-B182)/10</f>
-        <v>31.48600370390464</v>
+        <v>29.139413003510249</v>
       </c>
       <c r="D181" s="75">
         <v>10</v>
       </c>
       <c r="E181">
         <f t="shared" ref="E181:E189" si="42">B181-C181</f>
-        <v>665.20500166286365</v>
+        <v>565.49776938533557</v>
       </c>
       <c r="F181">
         <f t="shared" ref="F181:F189" si="43">B181-2*C181</f>
-        <v>633.71899795895899</v>
+        <v>536.35835638182539</v>
       </c>
       <c r="G181">
         <f t="shared" ref="G181:G189" si="44">B181-3*C181</f>
-        <v>602.23299425505434</v>
+        <v>507.21894337831509</v>
       </c>
       <c r="H181">
         <f t="shared" ref="H181:H189" si="45">B181-4*C181</f>
-        <v>570.74699055114979</v>
+        <v>478.0795303748049</v>
       </c>
       <c r="I181">
         <f t="shared" ref="I181:I189" si="46">B181-5*C181</f>
-        <v>539.26098684724514</v>
+        <v>448.9401173712946</v>
       </c>
       <c r="J181">
         <f t="shared" ref="J181:J189" si="47">B181-6*C181</f>
-        <v>507.77498314334048</v>
+        <v>419.80070436778436</v>
       </c>
       <c r="K181">
         <f t="shared" ref="K181:K189" si="48">B181-7*C181</f>
-        <v>476.28897943943582</v>
+        <v>390.66129136427412</v>
       </c>
       <c r="L181">
         <f t="shared" ref="L181:L189" si="49">B181-8*C181</f>
-        <v>444.80297573553116</v>
+        <v>361.52187836076388</v>
       </c>
       <c r="M181">
         <f t="shared" ref="M181:M189" si="50">B181-9*C181</f>
-        <v>413.31697203162656</v>
+        <v>332.38246535725364</v>
       </c>
       <c r="N181" s="8">
         <f t="shared" ref="N181:N189" si="51">B181-10*C181</f>
-        <v>381.83096832772191</v>
+        <v>303.24305235374339</v>
       </c>
       <c r="Q181" s="78" t="e">
         <f t="shared" ref="Q181:Q190" si="52">R21</f>
@@ -24445,54 +24439,54 @@
     <row r="182" spans="2:29">
       <c r="B182" s="78">
         <f t="shared" si="29"/>
-        <v>381.83096832772191</v>
+        <v>303.24305235374339</v>
       </c>
       <c r="C182">
         <f t="shared" si="41"/>
-        <v>11.895581676525079</v>
+        <v>10.002638019109913</v>
       </c>
       <c r="D182" s="75">
         <v>20</v>
       </c>
       <c r="E182">
         <f t="shared" si="42"/>
-        <v>369.93538665119684</v>
+        <v>293.2404143346335</v>
       </c>
       <c r="F182">
         <f t="shared" si="43"/>
-        <v>358.03980497467177</v>
+        <v>283.23777631552355</v>
       </c>
       <c r="G182">
         <f t="shared" si="44"/>
-        <v>346.1442232981467</v>
+        <v>273.23513829641365</v>
       </c>
       <c r="H182">
         <f t="shared" si="45"/>
-        <v>334.24864162162157</v>
+        <v>263.23250027730376</v>
       </c>
       <c r="I182">
         <f t="shared" si="46"/>
-        <v>322.3530599450965</v>
+        <v>253.22986225819383</v>
       </c>
       <c r="J182">
         <f t="shared" si="47"/>
-        <v>310.45747826857144</v>
+        <v>243.22722423908391</v>
       </c>
       <c r="K182">
         <f t="shared" si="48"/>
-        <v>298.56189659204637</v>
+        <v>233.22458621997401</v>
       </c>
       <c r="L182">
         <f t="shared" si="49"/>
-        <v>286.6663149155213</v>
+        <v>223.22194820086409</v>
       </c>
       <c r="M182">
         <f t="shared" si="50"/>
-        <v>274.77073323899617</v>
+        <v>213.21931018175417</v>
       </c>
       <c r="N182" s="8">
         <f t="shared" si="51"/>
-        <v>262.8751515624711</v>
+        <v>203.21667216264427</v>
       </c>
       <c r="Q182" s="78" t="e">
         <f t="shared" si="52"/>
@@ -24549,54 +24543,54 @@
     <row r="183" spans="2:29">
       <c r="B183" s="78">
         <f t="shared" si="29"/>
-        <v>262.8751515624711</v>
+        <v>203.21667216264427</v>
       </c>
       <c r="C183">
         <f t="shared" si="41"/>
-        <v>6.2460399697267288</v>
+        <v>5.0448577578520117</v>
       </c>
       <c r="D183" s="75">
         <v>30</v>
       </c>
       <c r="E183">
         <f t="shared" si="42"/>
-        <v>256.62911159274438</v>
+        <v>198.17181440479226</v>
       </c>
       <c r="F183">
         <f t="shared" si="43"/>
-        <v>250.38307162301766</v>
+        <v>193.12695664694024</v>
       </c>
       <c r="G183">
         <f t="shared" si="44"/>
-        <v>244.13703165329093</v>
+        <v>188.08209888908823</v>
       </c>
       <c r="H183">
         <f t="shared" si="45"/>
-        <v>237.89099168356418</v>
+        <v>183.03724113123621</v>
       </c>
       <c r="I183">
         <f t="shared" si="46"/>
-        <v>231.64495171383746</v>
+        <v>177.9923833733842</v>
       </c>
       <c r="J183">
         <f t="shared" si="47"/>
-        <v>225.39891174411073</v>
+        <v>172.94752561553219</v>
       </c>
       <c r="K183">
         <f t="shared" si="48"/>
-        <v>219.15287177438401</v>
+        <v>167.9026678576802</v>
       </c>
       <c r="L183">
         <f t="shared" si="49"/>
-        <v>212.90683180465726</v>
+        <v>162.85781009982819</v>
       </c>
       <c r="M183">
         <f t="shared" si="50"/>
-        <v>206.66079183493054</v>
+        <v>157.81295234197617</v>
       </c>
       <c r="N183" s="8">
         <f t="shared" si="51"/>
-        <v>200.41475186520381</v>
+        <v>152.76809458412416</v>
       </c>
       <c r="Q183" s="78" t="e">
         <f t="shared" si="52"/>
@@ -24653,54 +24647,54 @@
     <row r="184" spans="2:29">
       <c r="B184" s="78">
         <f t="shared" si="29"/>
-        <v>200.41475186520381</v>
+        <v>152.76809458412416</v>
       </c>
       <c r="C184">
         <f t="shared" si="41"/>
-        <v>3.8377128485545398</v>
+        <v>3.0393427999316556</v>
       </c>
       <c r="D184" s="75">
         <v>40</v>
       </c>
       <c r="E184">
         <f t="shared" si="42"/>
-        <v>196.57703901664928</v>
+        <v>149.7287517841925</v>
       </c>
       <c r="F184">
         <f t="shared" si="43"/>
-        <v>192.73932616809472</v>
+        <v>146.68940898426084</v>
       </c>
       <c r="G184">
         <f t="shared" si="44"/>
-        <v>188.90161331954019</v>
+        <v>143.65006618432921</v>
       </c>
       <c r="H184">
         <f t="shared" si="45"/>
-        <v>185.06390047098566</v>
+        <v>140.61072338439755</v>
       </c>
       <c r="I184">
         <f t="shared" si="46"/>
-        <v>181.2261876224311</v>
+        <v>137.57138058446589</v>
       </c>
       <c r="J184">
         <f t="shared" si="47"/>
-        <v>177.38847477387657</v>
+        <v>134.53203778453423</v>
       </c>
       <c r="K184">
         <f t="shared" si="48"/>
-        <v>173.55076192532204</v>
+        <v>131.49269498460257</v>
       </c>
       <c r="L184">
         <f t="shared" si="49"/>
-        <v>169.7130490767675</v>
+        <v>128.4533521846709</v>
       </c>
       <c r="M184">
         <f t="shared" si="50"/>
-        <v>165.87533622821294</v>
+        <v>125.41400938473926</v>
       </c>
       <c r="N184" s="8">
         <f t="shared" si="51"/>
-        <v>162.03762337965841</v>
+        <v>122.3746665848076</v>
       </c>
       <c r="Q184" s="78" t="e">
         <f t="shared" si="52"/>
@@ -24757,54 +24751,54 @@
     <row r="185" spans="2:29">
       <c r="B185" s="78">
         <f t="shared" si="29"/>
-        <v>162.03762337965841</v>
+        <v>122.3746665848076</v>
       </c>
       <c r="C185">
         <f t="shared" si="41"/>
-        <v>2.5732138183517379</v>
+        <v>2.0310476409048079</v>
       </c>
       <c r="D185" s="75">
         <v>50</v>
       </c>
       <c r="E185">
         <f t="shared" si="42"/>
-        <v>159.46440956130667</v>
+        <v>120.3436189439028</v>
       </c>
       <c r="F185">
         <f t="shared" si="43"/>
-        <v>156.89119574295495</v>
+        <v>118.31257130299798</v>
       </c>
       <c r="G185">
         <f t="shared" si="44"/>
-        <v>154.3179819246032</v>
+        <v>116.28152366209318</v>
       </c>
       <c r="H185">
         <f t="shared" si="45"/>
-        <v>151.74476810625146</v>
+        <v>114.25047602118836</v>
       </c>
       <c r="I185">
         <f t="shared" si="46"/>
-        <v>149.17155428789971</v>
+        <v>112.21942838028356</v>
       </c>
       <c r="J185">
         <f t="shared" si="47"/>
-        <v>146.59834046954799</v>
+        <v>110.18838073937874</v>
       </c>
       <c r="K185">
         <f t="shared" si="48"/>
-        <v>144.02512665119625</v>
+        <v>108.15733309847394</v>
       </c>
       <c r="L185">
         <f t="shared" si="49"/>
-        <v>141.4519128328445</v>
+        <v>106.12628545756914</v>
       </c>
       <c r="M185">
         <f t="shared" si="50"/>
-        <v>138.87869901449278</v>
+        <v>104.09523781666432</v>
       </c>
       <c r="N185" s="8">
         <f t="shared" si="51"/>
-        <v>136.30548519614103</v>
+        <v>102.06419017575952</v>
       </c>
       <c r="Q185" s="78" t="e">
         <f t="shared" si="52"/>
@@ -24861,54 +24855,54 @@
     <row r="186" spans="2:29">
       <c r="B186" s="78">
         <f t="shared" si="29"/>
-        <v>136.30548519614103</v>
+        <v>102.06419017575952</v>
       </c>
       <c r="C186">
         <f t="shared" si="41"/>
-        <v>1.8680148069296436</v>
+        <v>1.4529936989100178</v>
       </c>
       <c r="D186" s="75">
         <v>60</v>
       </c>
       <c r="E186">
         <f t="shared" si="42"/>
-        <v>134.4374703892114</v>
+        <v>100.6111964768495</v>
       </c>
       <c r="F186">
         <f t="shared" si="43"/>
-        <v>132.56945558228176</v>
+        <v>99.158202777939479</v>
       </c>
       <c r="G186">
         <f t="shared" si="44"/>
-        <v>130.7014407753521</v>
+        <v>97.705209079029473</v>
       </c>
       <c r="H186">
         <f t="shared" si="45"/>
-        <v>128.83342596842246</v>
+        <v>96.252215380119452</v>
       </c>
       <c r="I186">
         <f t="shared" si="46"/>
-        <v>126.96541116149282</v>
+        <v>94.799221681209431</v>
       </c>
       <c r="J186">
         <f t="shared" si="47"/>
-        <v>125.09739635456317</v>
+        <v>93.346227982299411</v>
       </c>
       <c r="K186">
         <f t="shared" si="48"/>
-        <v>123.22938154763352</v>
+        <v>91.89323428338939</v>
       </c>
       <c r="L186">
         <f t="shared" si="49"/>
-        <v>121.36136674070389</v>
+        <v>90.440240584479383</v>
       </c>
       <c r="M186">
         <f t="shared" si="50"/>
-        <v>119.49335193377425</v>
+        <v>88.987246885569363</v>
       </c>
       <c r="N186" s="8">
         <f t="shared" si="51"/>
-        <v>117.6253371268446</v>
+        <v>87.534253186659342</v>
       </c>
       <c r="Q186" s="78" t="e">
         <f t="shared" si="52"/>
@@ -24965,54 +24959,54 @@
     <row r="187" spans="2:29">
       <c r="B187" s="78">
         <f t="shared" si="29"/>
-        <v>117.6253371268446</v>
+        <v>87.534253186659342</v>
       </c>
       <c r="C187">
         <f t="shared" si="41"/>
-        <v>1.6346542722605903</v>
+        <v>1.0909287475084894</v>
       </c>
       <c r="D187" s="75">
         <v>70</v>
       </c>
       <c r="E187">
         <f t="shared" si="42"/>
-        <v>115.99068285458401</v>
+        <v>86.443324439150857</v>
       </c>
       <c r="F187">
         <f t="shared" si="43"/>
-        <v>114.35602858232342</v>
+        <v>85.352395691642357</v>
       </c>
       <c r="G187">
         <f t="shared" si="44"/>
-        <v>112.72137431006283</v>
+        <v>84.261466944133872</v>
       </c>
       <c r="H187">
         <f t="shared" si="45"/>
-        <v>111.08672003780224</v>
+        <v>83.170538196625387</v>
       </c>
       <c r="I187">
         <f t="shared" si="46"/>
-        <v>109.45206576554165</v>
+        <v>82.079609449116901</v>
       </c>
       <c r="J187">
         <f t="shared" si="47"/>
-        <v>107.81741149328106</v>
+        <v>80.988680701608402</v>
       </c>
       <c r="K187">
         <f t="shared" si="48"/>
-        <v>106.18275722102047</v>
+        <v>79.897751954099917</v>
       </c>
       <c r="L187">
         <f t="shared" si="49"/>
-        <v>104.54810294875988</v>
+        <v>78.806823206591432</v>
       </c>
       <c r="M187">
         <f t="shared" si="50"/>
-        <v>102.91344867649929</v>
+        <v>77.715894459082932</v>
       </c>
       <c r="N187" s="8">
         <f t="shared" si="51"/>
-        <v>101.2787944042387</v>
+        <v>76.624965711574447</v>
       </c>
       <c r="Q187" s="78" t="e">
         <f t="shared" si="52"/>
@@ -25069,54 +25063,54 @@
     <row r="188" spans="2:29">
       <c r="B188" s="78">
         <f t="shared" si="29"/>
-        <v>101.2787944042387</v>
+        <v>76.624965711574447</v>
       </c>
       <c r="C188">
         <f t="shared" si="41"/>
-        <v>1.4799627297481392</v>
+        <v>0.84918179753542522</v>
       </c>
       <c r="D188" s="75">
         <v>80</v>
       </c>
       <c r="E188">
         <f t="shared" si="42"/>
-        <v>99.798831674490557</v>
+        <v>75.775783914039025</v>
       </c>
       <c r="F188">
         <f t="shared" si="43"/>
-        <v>98.31886894474242</v>
+        <v>74.926602116503602</v>
       </c>
       <c r="G188">
         <f t="shared" si="44"/>
-        <v>96.838906214994282</v>
+        <v>74.077420318968166</v>
       </c>
       <c r="H188">
         <f t="shared" si="45"/>
-        <v>95.358943485246144</v>
+        <v>73.228238521432743</v>
       </c>
       <c r="I188">
         <f t="shared" si="46"/>
-        <v>93.878980755497992</v>
+        <v>72.379056723897321</v>
       </c>
       <c r="J188">
         <f t="shared" si="47"/>
-        <v>92.399018025749854</v>
+        <v>71.529874926361899</v>
       </c>
       <c r="K188">
         <f t="shared" si="48"/>
-        <v>90.919055296001716</v>
+        <v>70.680693128826476</v>
       </c>
       <c r="L188">
         <f t="shared" si="49"/>
-        <v>89.439092566253578</v>
+        <v>69.83151133129104</v>
       </c>
       <c r="M188">
         <f t="shared" si="50"/>
-        <v>87.95912983650544</v>
+        <v>68.982329533755617</v>
       </c>
       <c r="N188" s="8">
         <f t="shared" si="51"/>
-        <v>86.479167106757302</v>
+        <v>68.133147736220195</v>
       </c>
       <c r="Q188" s="78" t="e">
         <f t="shared" si="52"/>
@@ -25173,54 +25167,54 @@
     <row r="189" spans="2:29">
       <c r="B189" s="78">
         <f t="shared" si="29"/>
-        <v>86.479167106757302</v>
+        <v>68.133147736220195</v>
       </c>
       <c r="C189">
         <f t="shared" si="41"/>
-        <v>1.1592791606003643</v>
+        <v>0.67976528246889456</v>
       </c>
       <c r="D189" s="75">
         <v>90</v>
       </c>
       <c r="E189">
         <f t="shared" si="42"/>
-        <v>85.319887946156939</v>
+        <v>67.453382453751303</v>
       </c>
       <c r="F189">
         <f t="shared" si="43"/>
-        <v>84.160608785556576</v>
+        <v>66.77361717128241</v>
       </c>
       <c r="G189">
         <f t="shared" si="44"/>
-        <v>83.001329624956213</v>
+        <v>66.093851888813518</v>
       </c>
       <c r="H189">
         <f t="shared" si="45"/>
-        <v>81.84205046435585</v>
+        <v>65.414086606344611</v>
       </c>
       <c r="I189">
         <f t="shared" si="46"/>
-        <v>80.682771303755487</v>
+        <v>64.734321323875719</v>
       </c>
       <c r="J189">
         <f t="shared" si="47"/>
-        <v>79.52349214315511</v>
+        <v>64.054556041406826</v>
       </c>
       <c r="K189">
         <f t="shared" si="48"/>
-        <v>78.364212982554747</v>
+        <v>63.374790758937934</v>
       </c>
       <c r="L189">
         <f t="shared" si="49"/>
-        <v>77.204933821954384</v>
+        <v>62.695025476469041</v>
       </c>
       <c r="M189">
         <f t="shared" si="50"/>
-        <v>76.045654661354021</v>
+        <v>62.015260194000142</v>
       </c>
       <c r="N189" s="8">
         <f t="shared" si="51"/>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="Q189" s="78" t="e">
         <f t="shared" si="52"/>
@@ -25277,7 +25271,7 @@
     <row r="190" spans="2:29">
       <c r="B190" s="78">
         <f t="shared" si="29"/>
-        <v>74.886375500753658</v>
+        <v>61.335494911531249</v>
       </c>
       <c r="N190" s="8"/>
       <c r="Q190" s="78" t="e">
@@ -25354,7 +25348,7 @@
       <c r="B192" s="7"/>
       <c r="C192" s="80">
         <f>Расчет!K33</f>
-        <v>74.8</v>
+        <v>20</v>
       </c>
       <c r="E192" s="71">
         <v>10</v>
@@ -26839,14 +26833,19 @@
       <c r="AC212" s="10"/>
     </row>
     <row r="215" spans="1:29" ht="16.5">
-      <c r="A215" s="336" t="s">
+      <c r="A215" s="332" t="s">
         <v>105</v>
       </c>
-      <c r="B215" s="336"/>
-      <c r="C215" s="336"/>
+      <c r="B215" s="332"/>
+      <c r="C215" s="332"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="M8:M15"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="M19:M26"/>
+    <mergeCell ref="M30:M37"/>
     <mergeCell ref="M41:M48"/>
     <mergeCell ref="A215:C215"/>
     <mergeCell ref="M52:M59"/>
@@ -26857,11 +26856,6 @@
     <mergeCell ref="M74:M81"/>
     <mergeCell ref="M85:M92"/>
     <mergeCell ref="M96:M103"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="M8:M15"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="M19:M26"/>
-    <mergeCell ref="M30:M37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
